--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2588.16</v>
+        <v>2522.06</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20637.34</v>
+        <v>20110.35</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9224.200000000001</v>
+        <v>8988.66</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3524.37</v>
+        <v>3434.37</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>36979.72</v>
+        <v>36035.41</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6881.74</v>
+        <v>6706.01</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2911.1</v>
+        <v>2836.77</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5267.97</v>
+        <v>5133.45</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10383.73</v>
+        <v>10118.57</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>868.3</v>
+        <v>846.13</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2152.02</v>
+        <v>2097.06</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>46873.82</v>
+        <v>45959.57</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7260.75</v>
+        <v>7119.13</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>833.5700000000001</v>
+        <v>817.3099999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1985.71</v>
+        <v>1946.98</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>31922.75</v>
+        <v>31300.11</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>904.99</v>
+        <v>887.34</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3487.35</v>
+        <v>3419.33</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5260.97</v>
+        <v>5158.36</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2439.49</v>
+        <v>2391.91</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9111.120000000001</v>
+        <v>8933.41</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7275.17</v>
+        <v>7133.27</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6759.16</v>
+        <v>6627.33</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4644.41</v>
+        <v>4553.82</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1490.25</v>
+        <v>1461.18</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>8309.049999999999</v>
+        <v>8146.99</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4038.35</v>
+        <v>3959.58</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3833.99</v>
+        <v>3759.21</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>27710.23</v>
+        <v>27169.75</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1715.76</v>
+        <v>1682.3</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>11646.06</v>
+        <v>11418.9</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2194.99</v>
+        <v>2152.18</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3954.49</v>
+        <v>3861.98</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>802.02</v>
+        <v>783.25</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>794.4299999999999</v>
+        <v>775.85</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2440.91</v>
+        <v>2383.81</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>13527.54</v>
+        <v>13211.09</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>9344.82</v>
+        <v>9126.219999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3462.6</v>
+        <v>3381.6</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3881.65</v>
+        <v>3790.85</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3268.49</v>
+        <v>3192.03</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7846.56</v>
+        <v>7663</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1849.01</v>
+        <v>1805.76</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7743</v>
+        <v>7561.87</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8023.39</v>
+        <v>7835.69</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>6915.36</v>
+        <v>6753.59</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>7371.82</v>
+        <v>7199.37</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>6209.21</v>
+        <v>6063.95</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2732.72</v>
+        <v>2668.8</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1259.65</v>
+        <v>1230.18</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>21464.58</v>
+        <v>20962.45</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>792.52</v>
+        <v>773.98</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>857.79</v>
+        <v>837.72</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3225.44</v>
+        <v>3179.2</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1037.12</v>
+        <v>1022.25</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>14555.18</v>
+        <v>14346.56</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8513.41</v>
+        <v>8391.379999999999</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3030.11</v>
+        <v>2986.68</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1835.99</v>
+        <v>1809.67</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2960.83</v>
+        <v>2918.39</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2758.07</v>
+        <v>2718.54</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7906.21</v>
+        <v>7792.89</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>36813.35</v>
+        <v>36285.7</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>5397.26</v>
+        <v>5319.9</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4714.42</v>
+        <v>4646.85</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2135.08</v>
+        <v>2104.48</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>7071.49</v>
+        <v>6970.13</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>27145.77</v>
+        <v>26756.69</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>8575.09</v>
+        <v>8452.190000000001</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>789.63</v>
+        <v>778.3099999999999</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3264.47</v>
+        <v>3217.68</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>9037.9</v>
+        <v>8908.360000000001</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>6146.78</v>
+        <v>6058.67</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>11852.54</v>
+        <v>11682.65</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3165.31</v>
+        <v>3119.94</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2399.48</v>
+        <v>2365.09</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>6456.4</v>
+        <v>6363.86</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2528.71</v>
+        <v>2496.62</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3605.44</v>
+        <v>3559.68</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2043.54</v>
+        <v>2017.6</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4705.78</v>
+        <v>4646.05</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>11715.98</v>
+        <v>11567.27</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>15195.01</v>
+        <v>15002.15</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2625.1</v>
+        <v>2591.78</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2649.33</v>
+        <v>2615.71</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>8218.879999999999</v>
+        <v>8114.56</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1554.75</v>
+        <v>1535.02</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>6461.36</v>
+        <v>6379.35</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3330.83</v>
+        <v>3288.55</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2627.69</v>
+        <v>2594.33</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5323.01</v>
+        <v>5255.44</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2454.57</v>
+        <v>2423.42</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2423.17</v>
+        <v>2392.41</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2396.67</v>
+        <v>2366.25</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>6548.51</v>
+        <v>6465.39</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>7863.19</v>
+        <v>7763.38</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3262.76</v>
+        <v>3221.34</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1985.65</v>
+        <v>1960.45</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>4560.48</v>
+        <v>4502.59</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2863.98</v>
+        <v>2827.63</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1756.19</v>
+        <v>1733.9</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2752.72</v>
+        <v>2717.78</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>6001.79</v>
+        <v>5925.61</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3010.92</v>
+        <v>2972.71</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>911.52</v>
+        <v>899.95</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2370.67</v>
+        <v>2340.58</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>48423.03</v>
+        <v>47808.41</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3567.53</v>
+        <v>3522.24</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>814.39</v>
+        <v>804.05</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2124.31</v>
+        <v>2097.35</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1306.76</v>
+        <v>1290.18</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3295.95</v>
+        <v>3254.11</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>48275.62</v>
+        <v>47662.87</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>4104.24</v>
+        <v>4052.14</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>7063.11</v>
+        <v>6973.46</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1702.34</v>
+        <v>1680.73</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2069.84</v>
+        <v>2043.57</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>20922.25</v>
+        <v>20656.69</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5080.37</v>
+        <v>5007.16</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>4818.39</v>
+        <v>4748.96</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2584.19</v>
+        <v>2546.95</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>74086.57000000001</v>
+        <v>73018.97</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3039.73</v>
+        <v>2995.93</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>6261.47</v>
+        <v>6171.24</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1184.58</v>
+        <v>1167.51</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2296.55</v>
+        <v>2263.45</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>6809.11</v>
+        <v>6710.99</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>827.92</v>
+        <v>815.99</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2765.47</v>
+        <v>2725.62</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3761.17</v>
+        <v>3706.97</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>4347.22</v>
+        <v>4284.57</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2108.16</v>
+        <v>2077.78</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>14172.65</v>
+        <v>13968.42</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>15985.79</v>
+        <v>15755.44</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>7406.66</v>
+        <v>7299.93</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3482.76</v>
+        <v>3432.57</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>18093.01</v>
+        <v>17832.29</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>4378.64</v>
+        <v>4315.54</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1925.07</v>
+        <v>1897.33</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>5144.91</v>
+        <v>5070.78</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>5725.41</v>
+        <v>5642.91</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4372.22</v>
+        <v>4309.21</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>17733.57</v>
+        <v>17478.03</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1102.81</v>
+        <v>1086.92</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>6394.69</v>
+        <v>6302.54</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>9096.129999999999</v>
+        <v>8965.049999999999</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>4111.25</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3698.7</v>
+        <v>3645.4</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>12295.03</v>
+        <v>12117.86</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2700.01</v>
+        <v>2665.11</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>9936.51</v>
+        <v>9808.09</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2419.44</v>
+        <v>2388.17</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>3916.68</v>
+        <v>3866.06</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>10759.5</v>
+        <v>10620.44</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2702.14</v>
+        <v>2667.21</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>9221.93</v>
+        <v>9102.75</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3924.86</v>
+        <v>3874.13</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2277.46</v>
+        <v>2248.02</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2713.39</v>
+        <v>2678.33</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>888.5</v>
+        <v>877.01</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1407.92</v>
+        <v>1389.73</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>10839.97</v>
+        <v>10699.87</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>60094.64</v>
+        <v>59317.95</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1009.65</v>
+        <v>996.61</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>3868.82</v>
+        <v>3818.82</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>15629.99</v>
+        <v>15427.98</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5134.19</v>
+        <v>5067.84</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>966.5</v>
+        <v>954</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>23794.82</v>
+        <v>23487.29</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>5887.63</v>
+        <v>5811.54</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1829.49</v>
+        <v>1805.85</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>4041.28</v>
+        <v>3989.05</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2497.8</v>
+        <v>2465.52</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2551.6</v>
+        <v>2518.62</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>3882.46</v>
+        <v>3832.28</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2879.41</v>
+        <v>2842.2</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>5382.45</v>
+        <v>5312.89</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3020.89</v>
+        <v>2981.84</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>24373.65</v>
+        <v>24058.64</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>8921.67</v>
+        <v>8806.360000000001</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>3677.16</v>
+        <v>3629.64</v>
       </c>
     </row>
     <row r="183">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2530.19</v>
+        <v>2497.49</v>
       </c>
     </row>
     <row r="184">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3226.86</v>
+        <v>3185.15</v>
       </c>
     </row>
     <row r="185">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3890.54</v>
+        <v>3840.25</v>
       </c>
     </row>
     <row r="186">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>4818.5</v>
+        <v>4756.23</v>
       </c>
     </row>
     <row r="187">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2267.3</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>14416.4</v>
+        <v>14230.08</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>7094.67</v>
+        <v>7002.98</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>13233.74</v>
+        <v>13062.71</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>10469.59</v>
+        <v>10334.28</v>
       </c>
     </row>
     <row r="192">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>3396.66</v>
+        <v>3352.76</v>
       </c>
     </row>
     <row r="193">
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1390.23</v>
+        <v>1372.26</v>
       </c>
     </row>
     <row r="194">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>7547.2</v>
+        <v>7532.33</v>
       </c>
     </row>
     <row r="195">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>7221.72</v>
+        <v>7207.5</v>
       </c>
     </row>
     <row r="196">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>6251.78</v>
+        <v>6239.47</v>
       </c>
     </row>
     <row r="197">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>3081.47</v>
+        <v>3075.4</v>
       </c>
     </row>
     <row r="198">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>13305.77</v>
+        <v>13279.56</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>795.37</v>
+        <v>793.8099999999999</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>4491.95</v>
+        <v>4483.1</v>
       </c>
     </row>
     <row r="201">
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>925.28</v>
+        <v>923.46</v>
       </c>
     </row>
     <row r="202">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1542.51</v>
+        <v>1539.47</v>
       </c>
     </row>
     <row r="203">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>3828.97</v>
+        <v>3821.43</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>3309.42</v>
+        <v>3302.9</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>789.6</v>
+        <v>788.04</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1083.2</v>
+        <v>1081.06</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>3993.39</v>
+        <v>3985.52</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>10761.57</v>
+        <v>10740.38</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1424.86</v>
+        <v>1422.06</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>11179.55</v>
+        <v>11157.54</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>6580.91</v>
+        <v>6567.95</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>8679.51</v>
+        <v>8662.42</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3035.54</v>
+        <v>3029.56</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>802.72</v>
+        <v>801.13</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>14576.22</v>
+        <v>14547.52</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>7196.54</v>
+        <v>7182.36</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>6616.87</v>
+        <v>6603.84</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>3952.33</v>
+        <v>3944.54</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>5791.65</v>
+        <v>5780.24</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>32734.62</v>
+        <v>32670.15</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2792.7</v>
+        <v>2787.2</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>9475.940000000001</v>
+        <v>9457.280000000001</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>12509.94</v>
+        <v>12485.31</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>21080.85</v>
+        <v>21039.34</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>8617.709999999999</v>
+        <v>8600.74</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2402.2</v>
+        <v>2397.47</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>5691.6</v>
+        <v>5680.39</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>10049.67</v>
+        <v>10029.88</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1349.94</v>
+        <v>1347.28</v>
       </c>
     </row>
     <row r="230">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>4449.59</v>
+        <v>4440.83</v>
       </c>
     </row>
     <row r="231">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>4267.07</v>
+        <v>4258.67</v>
       </c>
     </row>
     <row r="232">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>814.72</v>
+        <v>813.12</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1601.31</v>
+        <v>1598.16</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>3402.89</v>
+        <v>3396.19</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>10069.28</v>
+        <v>10049.45</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>18980.65</v>
+        <v>18943.27</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>7643.12</v>
+        <v>7628.07</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3280.2</v>
+        <v>3280.23</v>
       </c>
     </row>
     <row r="239">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>2861.56</v>
+        <v>2861.58</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2685.68</v>
+        <v>2685.7</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>8903.52</v>
+        <v>8903.58</v>
       </c>
     </row>
     <row r="242">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>13803.07</v>
+        <v>13803.16</v>
       </c>
     </row>
     <row r="243">
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>3108.05</v>
+        <v>3108.07</v>
       </c>
     </row>
     <row r="244">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1955.9</v>
+        <v>1955.92</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2544.33</v>
+        <v>2544.35</v>
       </c>
     </row>
     <row r="246">
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>3965.92</v>
+        <v>3965.95</v>
       </c>
     </row>
     <row r="247">
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>2496.49</v>
+        <v>2496.5</v>
       </c>
     </row>
     <row r="248">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1138.95</v>
+        <v>1138.96</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1483.91</v>
+        <v>1483.92</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2967.95</v>
+        <v>2967.97</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2633.5</v>
+        <v>2633.52</v>
       </c>
     </row>
     <row r="252">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2822.92</v>
+        <v>2822.94</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>5524.83</v>
+        <v>5524.87</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>3141.86</v>
+        <v>3141.88</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>3187.05</v>
+        <v>3187.07</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>3136.89</v>
+        <v>3136.91</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>9557.82</v>
+        <v>9557.879999999999</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>4412.59</v>
+        <v>4412.62</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>7815.29</v>
+        <v>7815.34</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>10096.91</v>
+        <v>10096.97</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>4070.93</v>
+        <v>4070.95</v>
       </c>
     </row>
     <row r="262">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>2644.48</v>
+        <v>2644.5</v>
       </c>
     </row>
     <row r="264">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>5071.59</v>
+        <v>5071.62</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>7831.15</v>
+        <v>7831.2</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>21527.45</v>
+        <v>21527.59</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>75177.53</v>
+        <v>75178.02</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>805.2</v>
+        <v>805.21</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>3578.77</v>
+        <v>3578.79</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>15665.8</v>
+        <v>15665.9</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>9505.290000000001</v>
+        <v>9505.35</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>22654.14</v>
+        <v>22654.29</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>4617.42</v>
+        <v>4617.45</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>7261.22</v>
+        <v>7261.26</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>2489.94</v>
+        <v>2489.96</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>1088.53</v>
+        <v>1088.54</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>40697.43</v>
+        <v>40697.69</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>2302.47</v>
+        <v>2302.48</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>5297.05</v>
+        <v>5297.09</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1765.88</v>
+        <v>1765.89</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2378.75</v>
+        <v>2378.77</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1392.58</v>
+        <v>1392.59</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>5859.75</v>
+        <v>5859.78</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2451.2</v>
+        <v>2451.21</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>6084.18</v>
+        <v>6084.22</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>2711.31</v>
+        <v>2711.33</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>10649.16</v>
+        <v>10649.23</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2677.15</v>
+        <v>2677.16</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2260.04</v>
+        <v>2260.05</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1242.49</v>
+        <v>1242.5</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1118.99</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2944.42</v>
+        <v>2944.44</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1028.75</v>
+        <v>1028.76</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>5258.35</v>
+        <v>5258.38</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2296.42</v>
+        <v>2296.44</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>8363.59</v>
+        <v>8363.65</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2426.48</v>
+        <v>2426.5</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>6263.95</v>
+        <v>6263.99</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>3056.51</v>
+        <v>3056.53</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>5537.1</v>
+        <v>5544.79</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>4836.24</v>
+        <v>4842.95</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>22596.07</v>
+        <v>22627.44</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>9853.25</v>
+        <v>9866.93</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>7122.22</v>
+        <v>7132.1</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>12599.63</v>
+        <v>12617.12</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>790.13</v>
+        <v>791.23</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1164.71</v>
+        <v>1166.32</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>10507.84</v>
+        <v>10522.43</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>5890.6</v>
+        <v>5898.78</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2382.9</v>
+        <v>2386.21</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>5616.1</v>
+        <v>5623.9</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>5225.71</v>
+        <v>5232.97</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>4807.46</v>
+        <v>4814.14</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>4836.65</v>
+        <v>4843.36</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2663.28</v>
+        <v>2666.98</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>3444.27</v>
+        <v>3449.05</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1225.75</v>
+        <v>1227.45</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1552.85</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>2710.64</v>
+        <v>2714.4</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>5102</v>
+        <v>5109.09</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2834.04</v>
+        <v>2837.97</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>58424.17</v>
+        <v>58505.29</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>35858.29</v>
+        <v>35908.08</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>6773.45</v>
+        <v>6782.85</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>3435.25</v>
+        <v>3440.02</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>4365.55</v>
+        <v>4371.61</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>6586.77</v>
+        <v>6595.92</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>3869.41</v>
+        <v>3874.78</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>6610.54</v>
+        <v>6619.72</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>4650.24</v>
+        <v>4656.7</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>60452.06</v>
+        <v>60536</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>15674.49</v>
+        <v>15696.26</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>2475.13</v>
+        <v>2478.57</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3660.87</v>
+        <v>3665.95</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>2005.91</v>
+        <v>2008.69</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>3530.92</v>
+        <v>3535.82</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>14545.57</v>
+        <v>14565.77</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>8336.879999999999</v>
+        <v>8348.459999999999</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>5453.95</v>
+        <v>5461.52</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>1886.84</v>
+        <v>1885.55</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>5615.18</v>
+        <v>5611.34</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>3692.76</v>
+        <v>3690.24</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2681.23</v>
+        <v>2679.39</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>2743.55</v>
+        <v>2741.67</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>3199.47</v>
+        <v>3197.28</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>5825.29</v>
+        <v>5821.31</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>4187.24</v>
+        <v>4184.38</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>3940.93</v>
+        <v>3938.24</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>3342.71</v>
+        <v>3340.43</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>16033.41</v>
+        <v>16022.46</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>3261.89</v>
+        <v>3259.67</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2396.97</v>
+        <v>2395.33</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>10928.7</v>
+        <v>10921.24</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1478.67</v>
+        <v>1477.66</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>6573.79</v>
+        <v>6569.3</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>40665.1</v>
+        <v>40637.32</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>6209.78</v>
+        <v>6205.54</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1170.84</v>
+        <v>1170.04</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>8197.719999999999</v>
+        <v>8192.120000000001</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>2612.35</v>
+        <v>2610.56</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>4342.19</v>
+        <v>4339.22</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1256.82</v>
+        <v>1255.96</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2824.04</v>
+        <v>2822.11</v>
       </c>
     </row>
     <row r="365">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>851.34</v>
+        <v>850.76</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>6083.77</v>
+        <v>6079.62</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>8938.809999999999</v>
+        <v>8932.700000000001</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>2824</v>
+        <v>2822.07</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>1644.54</v>
+        <v>1643.41</v>
       </c>
     </row>
     <row r="370">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>2127.72</v>
+        <v>2126.27</v>
       </c>
     </row>
     <row r="371">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>42957.41</v>
+        <v>42928.06</v>
       </c>
     </row>
     <row r="372">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>6482.69</v>
+        <v>6478.26</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>5708.58</v>
+        <v>5704.68</v>
       </c>
     </row>
     <row r="374">
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>14790.81</v>
+        <v>14780.7</v>
       </c>
     </row>
     <row r="375">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>7250.94</v>
+        <v>7245.98</v>
       </c>
     </row>
     <row r="376">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>4096.57</v>
+        <v>4093.77</v>
       </c>
     </row>
     <row r="377">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>4522.08</v>
+        <v>4518.99</v>
       </c>
     </row>
     <row r="378">
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>7201.6</v>
+        <v>7196.68</v>
       </c>
     </row>
     <row r="379">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>67848.78999999999</v>
+        <v>67802.44</v>
       </c>
     </row>
     <row r="380">
@@ -23631,7 +23631,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>5365.41</v>
+        <v>5361.74</v>
       </c>
     </row>
     <row r="381">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2619.45</v>
+        <v>2617.66</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>851.41</v>
+        <v>850.83</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>7541.82</v>
+        <v>7536.67</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>2270.04</v>
+        <v>2268.49</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1525.25</v>
+        <v>1524.21</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>1809.4</v>
+        <v>1808.16</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>7526.73</v>
+        <v>7521.59</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>2608.85</v>
+        <v>2599.9</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>1722.47</v>
+        <v>1716.56</v>
       </c>
     </row>
     <row r="390">
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>3101.83</v>
+        <v>3091.19</v>
       </c>
     </row>
     <row r="391">
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>12428.17</v>
+        <v>12385.52</v>
       </c>
     </row>
     <row r="392">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>4226.41</v>
+        <v>4211.91</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>28360.87</v>
+        <v>28263.53</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>15342.82</v>
+        <v>15290.16</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2856.92</v>
+        <v>2847.11</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>10711.96</v>
+        <v>10675.2</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>862.65</v>
+        <v>859.6900000000001</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>2217.15</v>
+        <v>2209.54</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>6574.74</v>
+        <v>6552.17</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>2050.21</v>
+        <v>2043.17</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1087.48</v>
+        <v>1083.74</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>4688.16</v>
+        <v>4672.07</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>2601.04</v>
+        <v>2592.12</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>3473.46</v>
+        <v>3461.54</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>2505.96</v>
+        <v>2497.36</v>
       </c>
     </row>
     <row r="406">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>2708.55</v>
+        <v>2699.25</v>
       </c>
     </row>
     <row r="407">
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>1076.29</v>
+        <v>1072.6</v>
       </c>
     </row>
     <row r="408">
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>4459.66</v>
+        <v>4444.35</v>
       </c>
     </row>
     <row r="409">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>2954.25</v>
+        <v>2944.11</v>
       </c>
     </row>
     <row r="410">
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>8695.15</v>
+        <v>8665.299999999999</v>
       </c>
     </row>
     <row r="411">
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>5486.87</v>
+        <v>5468.04</v>
       </c>
     </row>
     <row r="412">
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1493.08</v>
+        <v>1487.96</v>
       </c>
     </row>
     <row r="413">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>794.7</v>
+        <v>791.97</v>
       </c>
     </row>
     <row r="414">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>6106.97</v>
+        <v>6086.01</v>
       </c>
     </row>
     <row r="415">
@@ -25766,7 +25766,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>8192.360000000001</v>
+        <v>8164.24</v>
       </c>
     </row>
     <row r="416">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1142.39</v>
+        <v>1138.47</v>
       </c>
     </row>
     <row r="417">
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>16232.01</v>
+        <v>16176.3</v>
       </c>
     </row>
     <row r="418">
@@ -25949,7 +25949,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>12334.43</v>
+        <v>12292.1</v>
       </c>
     </row>
     <row r="419">
@@ -26010,7 +26010,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>4439.95</v>
+        <v>4424.71</v>
       </c>
     </row>
     <row r="420">
@@ -26071,7 +26071,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>20624.12</v>
+        <v>20553.33</v>
       </c>
     </row>
     <row r="421">
@@ -26132,7 +26132,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>2991.43</v>
+        <v>2981.16</v>
       </c>
     </row>
     <row r="422">
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>2949.97</v>
+        <v>2939.85</v>
       </c>
     </row>
     <row r="423">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>821.51</v>
+        <v>818.6900000000001</v>
       </c>
     </row>
     <row r="424">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>10892.62</v>
+        <v>10855.23</v>
       </c>
     </row>
     <row r="425">
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>2424.48</v>
+        <v>2411.68</v>
       </c>
     </row>
     <row r="426">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>8359.940000000001</v>
+        <v>8315.780000000001</v>
       </c>
     </row>
     <row r="427">
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>1895.32</v>
+        <v>1885.31</v>
       </c>
     </row>
     <row r="428">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>8624.07</v>
+        <v>8578.51</v>
       </c>
     </row>
     <row r="429">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>2236.87</v>
+        <v>2225.05</v>
       </c>
     </row>
     <row r="430">
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>9304.059999999999</v>
+        <v>9254.91</v>
       </c>
     </row>
     <row r="431">
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>4485.92</v>
+        <v>4462.22</v>
       </c>
     </row>
     <row r="432">
@@ -26803,7 +26803,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2558.95</v>
+        <v>2545.43</v>
       </c>
     </row>
     <row r="433">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>35200.62</v>
+        <v>35014.67</v>
       </c>
     </row>
     <row r="434">
@@ -26925,7 +26925,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>16152.01</v>
+        <v>16066.69</v>
       </c>
     </row>
     <row r="435">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>32924.84</v>
+        <v>32750.91</v>
       </c>
     </row>
     <row r="436">
@@ -27047,7 +27047,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>10631.35</v>
+        <v>10575.19</v>
       </c>
     </row>
     <row r="437">
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>2653.31</v>
+        <v>2639.3</v>
       </c>
     </row>
     <row r="438">
@@ -27169,7 +27169,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>1725.79</v>
+        <v>1716.67</v>
       </c>
     </row>
     <row r="439">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>4601.33</v>
+        <v>4577.03</v>
       </c>
     </row>
     <row r="440">
@@ -27291,7 +27291,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>3668.41</v>
+        <v>3649.03</v>
       </c>
     </row>
     <row r="441">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>799.16</v>
+        <v>794.9400000000001</v>
       </c>
     </row>
     <row r="442">
@@ -27413,7 +27413,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>2262.32</v>
+        <v>2250.37</v>
       </c>
     </row>
     <row r="443">
@@ -27474,7 +27474,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>3157.45</v>
+        <v>3140.77</v>
       </c>
     </row>
     <row r="444">
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>1439.46</v>
+        <v>1431.85</v>
       </c>
     </row>
     <row r="445">
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>11235.74</v>
+        <v>11176.39</v>
       </c>
     </row>
     <row r="446">
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>16711.8</v>
+        <v>16623.52</v>
       </c>
     </row>
     <row r="447">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>10753.94</v>
+        <v>10697.13</v>
       </c>
     </row>
     <row r="448">
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>3331.25</v>
+        <v>3313.66</v>
       </c>
     </row>
     <row r="449">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>5397.56</v>
+        <v>5369.05</v>
       </c>
     </row>
     <row r="450">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>3607.88</v>
+        <v>3588.82</v>
       </c>
     </row>
     <row r="451">
@@ -27962,7 +27962,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>73872.78999999999</v>
+        <v>73482.56</v>
       </c>
     </row>
     <row r="452">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>3348.96</v>
+        <v>3331.27</v>
       </c>
     </row>
     <row r="453">
@@ -28084,7 +28084,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>4236.87</v>
+        <v>4214.49</v>
       </c>
     </row>
     <row r="454">
@@ -28145,7 +28145,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>15245.78</v>
+        <v>15165.25</v>
       </c>
     </row>
     <row r="455">
@@ -28206,7 +28206,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2704.04</v>
+        <v>2689.76</v>
       </c>
     </row>
     <row r="456">
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1762.39</v>
+        <v>1753.08</v>
       </c>
     </row>
     <row r="457">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>1668.04</v>
+        <v>1659.23</v>
       </c>
     </row>
     <row r="458">
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>4779.14</v>
+        <v>4753.89</v>
       </c>
     </row>
     <row r="459">
@@ -28450,7 +28450,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>2312.22</v>
+        <v>2300.01</v>
       </c>
     </row>
     <row r="460">
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>3689.46</v>
+        <v>3669.97</v>
       </c>
     </row>
     <row r="461">
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>4750.49</v>
+        <v>4725.4</v>
       </c>
     </row>
     <row r="462">
@@ -28633,7 +28633,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>8426.030000000001</v>
+        <v>8381.51</v>
       </c>
     </row>
     <row r="463">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>3757.5</v>
+        <v>3737.65</v>
       </c>
     </row>
     <row r="464">
@@ -28755,7 +28755,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>6360.82</v>
+        <v>6327.22</v>
       </c>
     </row>
     <row r="465">
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>40991.98</v>
+        <v>40775.44</v>
       </c>
     </row>
     <row r="466">
@@ -28877,7 +28877,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>2124.31</v>
+        <v>2113.09</v>
       </c>
     </row>
     <row r="467">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>31493.15</v>
+        <v>31326.78</v>
       </c>
     </row>
     <row r="468">
@@ -28999,7 +28999,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>2034.13</v>
+        <v>2023.38</v>
       </c>
     </row>
     <row r="469">
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>2563.83</v>
+        <v>2550.28</v>
       </c>
     </row>
     <row r="470">
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>2376.13</v>
+        <v>2363.58</v>
       </c>
     </row>
     <row r="471">
@@ -29182,7 +29182,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>3534.46</v>
+        <v>3515.79</v>
       </c>
     </row>
     <row r="472">
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>16013.28</v>
+        <v>15928.69</v>
       </c>
     </row>
     <row r="473">
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>3995.61</v>
+        <v>3974.51</v>
       </c>
     </row>
     <row r="474">
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>21402.54</v>
+        <v>21289.48</v>
       </c>
     </row>
     <row r="475">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>3387.16</v>
+        <v>3369.27</v>
       </c>
     </row>
     <row r="476">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>7588.16</v>
+        <v>7548.08</v>
       </c>
     </row>
     <row r="477">
@@ -29548,7 +29548,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>2477.41</v>
+        <v>2464.33</v>
       </c>
     </row>
     <row r="478">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>2705.07</v>
+        <v>2690.78</v>
       </c>
     </row>
     <row r="479">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>4761.72</v>
+        <v>4736.57</v>
       </c>
     </row>
     <row r="480">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>2941.28</v>
+        <v>2925.74</v>
       </c>
     </row>
     <row r="481">
@@ -29792,7 +29792,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>7857.41</v>
+        <v>7815.91</v>
       </c>
     </row>
     <row r="482">
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>11000.32</v>
+        <v>10942.22</v>
       </c>
     </row>
     <row r="483">
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>1138.73</v>
+        <v>1132.71</v>
       </c>
     </row>
     <row r="484">
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>3806.8</v>
+        <v>3786.69</v>
       </c>
     </row>
     <row r="485">
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>6173.43</v>
+        <v>6140.82</v>
       </c>
     </row>
     <row r="486">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>15765.84</v>
+        <v>15682.56</v>
       </c>
     </row>
     <row r="487">
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>807.3099999999999</v>
+        <v>803.04</v>
       </c>
     </row>
     <row r="488">
@@ -30219,7 +30219,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>6038.24</v>
+        <v>6006.34</v>
       </c>
     </row>
     <row r="489">
@@ -30280,7 +30280,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>5872.38</v>
+        <v>5841.36</v>
       </c>
     </row>
     <row r="490">
@@ -30341,7 +30341,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1223.23</v>
+        <v>1215.56</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>18752.52</v>
+        <v>18635</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>7771.6</v>
+        <v>7722.9</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1875.53</v>
+        <v>1863.78</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>2867.17</v>
+        <v>2849.21</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>3188.89</v>
+        <v>3168.91</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>3391.84</v>
+        <v>3370.59</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>2685.01</v>
+        <v>2668.18</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>5267.97</v>
+        <v>5234.96</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>1963.9</v>
+        <v>1951.59</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>13497.06</v>
+        <v>13412.48</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>3688.57</v>
+        <v>3665.46</v>
       </c>
     </row>
     <row r="502">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>887.6900000000001</v>
+        <v>882.13</v>
       </c>
     </row>
     <row r="503">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>2377.12</v>
+        <v>2362.22</v>
       </c>
     </row>
     <row r="504">
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>3626.93</v>
+        <v>3604.2</v>
       </c>
     </row>
     <row r="505">
@@ -31256,7 +31256,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>3824.77</v>
+        <v>3800.81</v>
       </c>
     </row>
     <row r="506">
@@ -31317,7 +31317,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>9846.15</v>
+        <v>9784.450000000001</v>
       </c>
     </row>
     <row r="507">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>5182.46</v>
+        <v>5149.99</v>
       </c>
     </row>
     <row r="508">
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>15616.03</v>
+        <v>15518.17</v>
       </c>
     </row>
     <row r="509">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>1146.97</v>
+        <v>1139.78</v>
       </c>
     </row>
     <row r="510">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>5950.3</v>
+        <v>5913.01</v>
       </c>
     </row>
     <row r="511">
@@ -31622,7 +31622,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>6579.49</v>
+        <v>6538.26</v>
       </c>
     </row>
     <row r="512">
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>2152.58</v>
+        <v>2139.09</v>
       </c>
     </row>
     <row r="513">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>7996.06</v>
+        <v>7945.96</v>
       </c>
     </row>
     <row r="514">
@@ -31805,7 +31805,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>1906.77</v>
+        <v>1894.82</v>
       </c>
     </row>
     <row r="515">
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>1147.51</v>
+        <v>1140.32</v>
       </c>
     </row>
     <row r="516">
@@ -31927,7 +31927,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>2617.27</v>
+        <v>2600.87</v>
       </c>
     </row>
     <row r="517">
@@ -31988,7 +31988,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>3064.72</v>
+        <v>3045.51</v>
       </c>
     </row>
     <row r="518">
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>7797.76</v>
+        <v>7748.9</v>
       </c>
     </row>
     <row r="519">
@@ -32110,7 +32110,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>4510.92</v>
+        <v>4482.65</v>
       </c>
     </row>
     <row r="520">
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>6208.13</v>
+        <v>6169.23</v>
       </c>
     </row>
     <row r="521">
@@ -32232,7 +32232,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>3579.83</v>
+        <v>3557.4</v>
       </c>
     </row>
     <row r="522">
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>5075.58</v>
+        <v>5043.77</v>
       </c>
     </row>
     <row r="523">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>2095.95</v>
+        <v>2082.81</v>
       </c>
     </row>
     <row r="524">
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>3013.5</v>
+        <v>2994.62</v>
       </c>
     </row>
     <row r="525">
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>8763.790000000001</v>
+        <v>8708.870000000001</v>
       </c>
     </row>
     <row r="526">
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>27921.08</v>
+        <v>27746.11</v>
       </c>
     </row>
     <row r="527">
@@ -32598,7 +32598,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>5693.51</v>
+        <v>5657.83</v>
       </c>
     </row>
     <row r="528">
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>2955.58</v>
+        <v>2937.06</v>
       </c>
     </row>
     <row r="529">
@@ -32720,7 +32720,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>6633.56</v>
+        <v>6591.99</v>
       </c>
     </row>
     <row r="530">
@@ -32781,7 +32781,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>809.85</v>
+        <v>804.78</v>
       </c>
     </row>
     <row r="531">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>5575.99</v>
+        <v>5541.04</v>
       </c>
     </row>
     <row r="532">
@@ -32903,7 +32903,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>944.14</v>
+        <v>938.23</v>
       </c>
     </row>
     <row r="533">
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>1568.64</v>
+        <v>1558.81</v>
       </c>
     </row>
     <row r="534">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>11910.74</v>
+        <v>11836.1</v>
       </c>
     </row>
     <row r="535">
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>5375.29</v>
+        <v>5341.61</v>
       </c>
     </row>
     <row r="536">
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>5252.7</v>
+        <v>5219.78</v>
       </c>
     </row>
     <row r="537">
@@ -33208,7 +33208,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>11768.05</v>
+        <v>11845.18</v>
       </c>
     </row>
     <row r="538">
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>39427.82</v>
+        <v>39686.22</v>
       </c>
     </row>
     <row r="539">
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>1056.17</v>
+        <v>1063.09</v>
       </c>
     </row>
     <row r="540">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>6825.78</v>
+        <v>6870.52</v>
       </c>
     </row>
     <row r="541">
@@ -33452,7 +33452,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>3424.87</v>
+        <v>3447.32</v>
       </c>
     </row>
     <row r="542">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>5882.92</v>
+        <v>5921.48</v>
       </c>
     </row>
     <row r="543">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>2537.61</v>
+        <v>2554.24</v>
       </c>
     </row>
     <row r="544">
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>4278.62</v>
+        <v>4306.66</v>
       </c>
     </row>
     <row r="545">
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>9833.700000000001</v>
+        <v>9898.15</v>
       </c>
     </row>
     <row r="546">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>32945.35</v>
+        <v>33161.27</v>
       </c>
     </row>
     <row r="547">
@@ -33818,7 +33818,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>4978.94</v>
+        <v>5011.57</v>
       </c>
     </row>
     <row r="548">
@@ -33879,7 +33879,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>29148.99</v>
+        <v>29340.03</v>
       </c>
     </row>
     <row r="549">
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>2302.04</v>
+        <v>2317.13</v>
       </c>
     </row>
     <row r="550">
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>14594.03</v>
+        <v>14689.67</v>
       </c>
     </row>
     <row r="551">
@@ -34062,7 +34062,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>2739.39</v>
+        <v>2757.35</v>
       </c>
     </row>
     <row r="552">
@@ -34123,7 +34123,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>791.75</v>
+        <v>796.9400000000001</v>
       </c>
     </row>
     <row r="553">
@@ -34184,7 +34184,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>1535.74</v>
+        <v>1545.81</v>
       </c>
     </row>
     <row r="554">
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>1001.58</v>
+        <v>1008.14</v>
       </c>
     </row>
     <row r="555">
@@ -34306,7 +34306,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>3393.8</v>
+        <v>3416.04</v>
       </c>
     </row>
     <row r="556">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>3930.92</v>
+        <v>3956.68</v>
       </c>
     </row>
     <row r="557">
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>6095.76</v>
+        <v>6135.71</v>
       </c>
     </row>
     <row r="558">
@@ -34489,7 +34489,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>4859.88</v>
+        <v>4891.74</v>
       </c>
     </row>
     <row r="559">
@@ -34550,7 +34550,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>5414.99</v>
+        <v>5450.48</v>
       </c>
     </row>
     <row r="560">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>4122.62</v>
+        <v>4149.64</v>
       </c>
     </row>
     <row r="561">
@@ -34672,7 +34672,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>3231.57</v>
+        <v>3252.75</v>
       </c>
     </row>
     <row r="562">
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>2140.47</v>
+        <v>2154.5</v>
       </c>
     </row>
     <row r="563">
@@ -34794,7 +34794,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>3247.32</v>
+        <v>3268.6</v>
       </c>
     </row>
     <row r="564">
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>32229.05</v>
+        <v>32440.27</v>
       </c>
     </row>
     <row r="565">
@@ -34916,7 +34916,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>5013.27</v>
+        <v>5046.13</v>
       </c>
     </row>
     <row r="566">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>7064.34</v>
+        <v>7110.64</v>
       </c>
     </row>
     <row r="567">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>2665.1</v>
+        <v>2682.57</v>
       </c>
     </row>
     <row r="568">
@@ -35099,7 +35099,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>7236.53</v>
+        <v>7283.96</v>
       </c>
     </row>
     <row r="569">
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>14580.21</v>
+        <v>14675.77</v>
       </c>
     </row>
     <row r="570">
@@ -35221,7 +35221,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>2795.85</v>
+        <v>2814.18</v>
       </c>
     </row>
     <row r="571">
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>4298.54</v>
+        <v>4326.71</v>
       </c>
     </row>
     <row r="572">
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>27353.09</v>
+        <v>27532.36</v>
       </c>
     </row>
     <row r="573">
@@ -35404,7 +35404,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>22719.84</v>
+        <v>22868.75</v>
       </c>
     </row>
     <row r="574">
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>5503.9</v>
+        <v>5539.97</v>
       </c>
     </row>
     <row r="575">
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>6269.28</v>
+        <v>6310.37</v>
       </c>
     </row>
     <row r="576">
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>4144.45</v>
+        <v>4171.61</v>
       </c>
     </row>
     <row r="577">
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>32592.77</v>
+        <v>32806.38</v>
       </c>
     </row>
     <row r="578">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>4900.19</v>
+        <v>4932.31</v>
       </c>
     </row>
     <row r="579">
@@ -35770,7 +35770,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>2395.74</v>
+        <v>2411.44</v>
       </c>
     </row>
     <row r="580">
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>2621.67</v>
+        <v>2638.86</v>
       </c>
     </row>
     <row r="581">
@@ -35892,7 +35892,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>2836.31</v>
+        <v>2854.9</v>
       </c>
     </row>
     <row r="582">
@@ -35953,7 +35953,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>6230.9</v>
+        <v>6271.74</v>
       </c>
     </row>
     <row r="583">
@@ -36014,7 +36014,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>3781.25</v>
+        <v>3806.03</v>
       </c>
     </row>
     <row r="584">
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>35834.5</v>
+        <v>36069.35</v>
       </c>
     </row>
     <row r="585">
@@ -36136,7 +36136,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>1115.67</v>
+        <v>1122.98</v>
       </c>
     </row>
     <row r="586">
@@ -36197,7 +36197,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>4010.85</v>
+        <v>4037.13</v>
       </c>
     </row>
     <row r="587">
@@ -36258,7 +36258,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>35598.82</v>
+        <v>35832.13</v>
       </c>
     </row>
     <row r="588">
@@ -36319,7 +36319,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>34926.42</v>
+        <v>35396.76</v>
       </c>
     </row>
     <row r="589">
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>5936.93</v>
+        <v>6016.88</v>
       </c>
     </row>
     <row r="590">
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>1146.07</v>
+        <v>1161.51</v>
       </c>
     </row>
     <row r="591">
@@ -36502,7 +36502,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>65238.91</v>
+        <v>66117.44</v>
       </c>
     </row>
     <row r="592">
@@ -36563,7 +36563,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>2483.75</v>
+        <v>2517.2</v>
       </c>
     </row>
     <row r="593">
@@ -36624,7 +36624,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>8792.5</v>
+        <v>8910.9</v>
       </c>
     </row>
     <row r="594">
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>38220.14</v>
+        <v>38734.83</v>
       </c>
     </row>
     <row r="595">
@@ -36746,7 +36746,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>2880.53</v>
+        <v>2919.32</v>
       </c>
     </row>
     <row r="596">
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>790.48</v>
+        <v>801.12</v>
       </c>
     </row>
     <row r="597">
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>813.65</v>
+        <v>824.6</v>
       </c>
     </row>
     <row r="598">
@@ -36929,7 +36929,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>5408.1</v>
+        <v>5480.92</v>
       </c>
     </row>
     <row r="599">
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>2108.16</v>
+        <v>2136.55</v>
       </c>
     </row>
     <row r="600">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>1539.58</v>
+        <v>1560.31</v>
       </c>
     </row>
     <row r="601">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>4796.21</v>
+        <v>4860.8</v>
       </c>
     </row>
     <row r="602">
@@ -37173,7 +37173,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>20897.02</v>
+        <v>21178.43</v>
       </c>
     </row>
     <row r="603">
@@ -37234,7 +37234,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>1219.56</v>
+        <v>1235.98</v>
       </c>
     </row>
     <row r="604">
@@ -37295,7 +37295,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>10934.28</v>
+        <v>11081.52</v>
       </c>
     </row>
     <row r="605">
@@ -37356,7 +37356,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>3559.89</v>
+        <v>3607.83</v>
       </c>
     </row>
     <row r="606">
@@ -37417,7 +37417,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>940.92</v>
+        <v>953.59</v>
       </c>
     </row>
     <row r="607">
@@ -37478,7 +37478,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>12645.06</v>
+        <v>12815.35</v>
       </c>
     </row>
     <row r="608">
@@ -37539,7 +37539,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>18119.93</v>
+        <v>18363.94</v>
       </c>
     </row>
     <row r="609">
@@ -37600,7 +37600,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>3106.81</v>
+        <v>3148.65</v>
       </c>
     </row>
     <row r="610">
@@ -37661,7 +37661,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>1166.48</v>
+        <v>1182.19</v>
       </c>
     </row>
     <row r="611">
@@ -37722,7 +37722,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>2713.29</v>
+        <v>2749.82</v>
       </c>
     </row>
     <row r="612">
@@ -37783,7 +37783,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>1635.91</v>
+        <v>1657.94</v>
       </c>
     </row>
     <row r="613">
@@ -37844,7 +37844,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>4452.17</v>
+        <v>4512.13</v>
       </c>
     </row>
     <row r="614">
@@ -37905,7 +37905,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>3841.44</v>
+        <v>3893.17</v>
       </c>
     </row>
     <row r="615">
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>1459.96</v>
+        <v>1479.62</v>
       </c>
     </row>
     <row r="616">
@@ -38027,7 +38027,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>2575.29</v>
+        <v>2609.97</v>
       </c>
     </row>
     <row r="617">
@@ -38088,7 +38088,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>5711.95</v>
+        <v>5788.87</v>
       </c>
     </row>
     <row r="618">
@@ -38149,7 +38149,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>1601.96</v>
+        <v>1623.53</v>
       </c>
     </row>
     <row r="619">
@@ -38210,7 +38210,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>5030.27</v>
+        <v>5098.01</v>
       </c>
     </row>
     <row r="620">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>29879.92</v>
+        <v>30282.3</v>
       </c>
     </row>
     <row r="621">
@@ -38332,7 +38332,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>16911.25</v>
+        <v>17138.98</v>
       </c>
     </row>
     <row r="622">
@@ -38393,7 +38393,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>3956.06</v>
+        <v>4009.33</v>
       </c>
     </row>
     <row r="623">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>9127.950000000001</v>
+        <v>9250.870000000001</v>
       </c>
     </row>
     <row r="624">
@@ -38515,7 +38515,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1434.03</v>
+        <v>1453.34</v>
       </c>
     </row>
     <row r="625">
@@ -38576,7 +38576,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>1359.76</v>
+        <v>1378.07</v>
       </c>
     </row>
     <row r="626">
@@ -38637,7 +38637,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>7194.01</v>
+        <v>7290.89</v>
       </c>
     </row>
     <row r="627">
@@ -38698,7 +38698,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>6490.52</v>
+        <v>6577.92</v>
       </c>
     </row>
     <row r="628">
@@ -38759,7 +38759,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>6158.57</v>
+        <v>6241.5</v>
       </c>
     </row>
     <row r="629">
@@ -38820,7 +38820,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>10472.41</v>
+        <v>10613.43</v>
       </c>
     </row>
     <row r="630">
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>1506.21</v>
+        <v>1526.49</v>
       </c>
     </row>
     <row r="631">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>2524.27</v>
+        <v>2558.26</v>
       </c>
     </row>
     <row r="632">
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>4529.31</v>
+        <v>4590.3</v>
       </c>
     </row>
     <row r="633">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>2328.94</v>
+        <v>2360.3</v>
       </c>
     </row>
     <row r="634">
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>2554.83</v>
+        <v>2589.23</v>
       </c>
     </row>
     <row r="635">
@@ -39186,7 +39186,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>40878.22</v>
+        <v>41428.7</v>
       </c>
     </row>
     <row r="636">
@@ -39247,7 +39247,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>5360.33</v>
+        <v>5432.52</v>
       </c>
     </row>
     <row r="637">
@@ -39308,7 +39308,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>2009.27</v>
+        <v>2036.33</v>
       </c>
     </row>
     <row r="638">
@@ -39369,7 +39369,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>3090.5</v>
+        <v>3132.12</v>
       </c>
     </row>
     <row r="639">
@@ -39430,7 +39430,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>65338.38</v>
+        <v>66218.25999999999</v>
       </c>
     </row>
     <row r="640">
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>1519.59</v>
+        <v>1540.05</v>
       </c>
     </row>
     <row r="641">
@@ -39552,7 +39552,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>9513.1</v>
+        <v>9641.209999999999</v>
       </c>
     </row>
     <row r="642">
@@ -39613,7 +39613,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>58768.91</v>
+        <v>59560.32</v>
       </c>
     </row>
     <row r="643">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>78651.75</v>
+        <v>79710.91</v>
       </c>
     </row>
     <row r="644">
@@ -39735,7 +39735,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>20024.67</v>
+        <v>20294.33</v>
       </c>
     </row>
     <row r="645">
@@ -39796,7 +39796,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>12297.01</v>
+        <v>12462.61</v>
       </c>
     </row>
     <row r="646">
@@ -39857,7 +39857,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>40608.04</v>
+        <v>41154.88</v>
       </c>
     </row>
     <row r="647">
@@ -39918,7 +39918,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>2695.78</v>
+        <v>2732.08</v>
       </c>
     </row>
     <row r="648">
@@ -39979,7 +39979,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>73446.31</v>
+        <v>74435.37</v>
       </c>
     </row>
     <row r="649">
@@ -40040,7 +40040,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>40273.1</v>
+        <v>40815.44</v>
       </c>
     </row>
     <row r="650">
@@ -40101,7 +40101,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>8001.28</v>
+        <v>8109.02</v>
       </c>
     </row>
     <row r="651">
@@ -40162,7 +40162,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>4615.25</v>
+        <v>4677.41</v>
       </c>
     </row>
     <row r="652">
@@ -40223,7 +40223,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>2192.31</v>
+        <v>2221.83</v>
       </c>
     </row>
     <row r="653">
@@ -40284,7 +40284,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>71953.64</v>
+        <v>72922.60000000001</v>
       </c>
     </row>
     <row r="654">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>6943.69</v>
+        <v>7037.2</v>
       </c>
     </row>
     <row r="655">
@@ -40406,7 +40406,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>6128.2</v>
+        <v>6221.5</v>
       </c>
     </row>
     <row r="656">
@@ -40467,7 +40467,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>30895.43</v>
+        <v>31365.78</v>
       </c>
     </row>
     <row r="657">
@@ -40528,7 +40528,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>1466.52</v>
+        <v>1488.85</v>
       </c>
     </row>
     <row r="658">
@@ -40589,7 +40589,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>74243.27</v>
+        <v>75373.55</v>
       </c>
     </row>
     <row r="659">
@@ -40650,7 +40650,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>3968.1</v>
+        <v>4028.51</v>
       </c>
     </row>
     <row r="660">
@@ -40711,7 +40711,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>2347.19</v>
+        <v>2382.92</v>
       </c>
     </row>
     <row r="661">
@@ -40772,7 +40772,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>2820.26</v>
+        <v>2863.2</v>
       </c>
     </row>
     <row r="662">
@@ -40833,7 +40833,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>20642.17</v>
+        <v>20956.42</v>
       </c>
     </row>
     <row r="663">
@@ -40894,7 +40894,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>4610.87</v>
+        <v>4681.06</v>
       </c>
     </row>
     <row r="664">
@@ -40955,7 +40955,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>50984.86</v>
+        <v>51761.06</v>
       </c>
     </row>
     <row r="665">
@@ -41016,7 +41016,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>2185.7</v>
+        <v>2218.98</v>
       </c>
     </row>
     <row r="666">
@@ -41077,7 +41077,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>18942.33</v>
+        <v>19230.71</v>
       </c>
     </row>
     <row r="667">
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>3545.91</v>
+        <v>3599.89</v>
       </c>
     </row>
     <row r="668">
@@ -41199,7 +41199,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>10275.46</v>
+        <v>10431.89</v>
       </c>
     </row>
     <row r="669">
@@ -41260,7 +41260,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>8624.870000000001</v>
+        <v>8756.18</v>
       </c>
     </row>
     <row r="670">
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>6032.15</v>
+        <v>6123.98</v>
       </c>
     </row>
     <row r="671">
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>4953.91</v>
+        <v>5029.32</v>
       </c>
     </row>
     <row r="672">
@@ -41443,7 +41443,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>2404.13</v>
+        <v>2440.73</v>
       </c>
     </row>
     <row r="673">
@@ -41504,7 +41504,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>1591.56</v>
+        <v>1615.79</v>
       </c>
     </row>
     <row r="674">
@@ -41565,7 +41565,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>1542.12</v>
+        <v>1565.6</v>
       </c>
     </row>
     <row r="675">
@@ -41626,7 +41626,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>2595.22</v>
+        <v>2634.73</v>
       </c>
     </row>
     <row r="676">
@@ -41687,7 +41687,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>2054.98</v>
+        <v>2086.27</v>
       </c>
     </row>
     <row r="677">
@@ -41748,7 +41748,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>8354.549999999999</v>
+        <v>8481.74</v>
       </c>
     </row>
     <row r="678">
@@ -41809,7 +41809,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>34062.77</v>
+        <v>34581.34</v>
       </c>
     </row>
     <row r="679">
@@ -41870,7 +41870,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>3450.34</v>
+        <v>3502.87</v>
       </c>
     </row>
     <row r="680">
@@ -41931,7 +41931,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>10823.5</v>
+        <v>10988.27</v>
       </c>
     </row>
     <row r="681">
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>4095.25</v>
+        <v>4157.6</v>
       </c>
     </row>
     <row r="682">
@@ -42053,7 +42053,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>9152.799999999999</v>
+        <v>9292.139999999999</v>
       </c>
     </row>
     <row r="683">
@@ -42114,7 +42114,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>7048.74</v>
+        <v>7156.05</v>
       </c>
     </row>
     <row r="684">
@@ -42175,7 +42175,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>3824.63</v>
+        <v>3882.85</v>
       </c>
     </row>
     <row r="685">
@@ -42236,7 +42236,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>2147.91</v>
+        <v>2180.61</v>
       </c>
     </row>
     <row r="686">
@@ -42297,7 +42297,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>1360.74</v>
+        <v>1381.46</v>
       </c>
     </row>
     <row r="687">
@@ -42358,7 +42358,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>21890.76</v>
+        <v>22224.03</v>
       </c>
     </row>
     <row r="688">
@@ -42419,7 +42419,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>4218.74</v>
+        <v>4282.97</v>
       </c>
     </row>
     <row r="689">
@@ -42480,7 +42480,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>2383.33</v>
+        <v>2419.62</v>
       </c>
     </row>
     <row r="690">
@@ -42541,7 +42541,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>11310.05</v>
+        <v>11482.23</v>
       </c>
     </row>
     <row r="691">
@@ -42602,7 +42602,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>2515.25</v>
+        <v>2553.54</v>
       </c>
     </row>
     <row r="692">
@@ -42663,7 +42663,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>832.14</v>
+        <v>844.8099999999999</v>
       </c>
     </row>
     <row r="693">
@@ -42724,7 +42724,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>10029.24</v>
+        <v>10181.92</v>
       </c>
     </row>
     <row r="694">
@@ -42785,7 +42785,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>4742.39</v>
+        <v>4814.59</v>
       </c>
     </row>
     <row r="695">
@@ -42846,7 +42846,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>2469.25</v>
+        <v>2506.84</v>
       </c>
     </row>
     <row r="696">
@@ -42907,7 +42907,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>2739.23</v>
+        <v>2780.93</v>
       </c>
     </row>
     <row r="697">
@@ -42968,7 +42968,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>2343.53</v>
+        <v>2379.21</v>
       </c>
     </row>
     <row r="698">
@@ -43029,7 +43029,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>2354.44</v>
+        <v>2390.28</v>
       </c>
     </row>
     <row r="699">
@@ -43090,7 +43090,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>3793.07</v>
+        <v>3850.82</v>
       </c>
     </row>
     <row r="700">
@@ -43151,7 +43151,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>3028.96</v>
+        <v>3075.08</v>
       </c>
     </row>
     <row r="701">
@@ -43212,7 +43212,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>1984.22</v>
+        <v>2014.43</v>
       </c>
     </row>
     <row r="702">
@@ -43273,7 +43273,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>1245.25</v>
+        <v>1264.2</v>
       </c>
     </row>
     <row r="703">
@@ -43334,7 +43334,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>1641.78</v>
+        <v>1666.77</v>
       </c>
     </row>
     <row r="704">
@@ -43395,7 +43395,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>2502.23</v>
+        <v>2540.32</v>
       </c>
     </row>
     <row r="705">
@@ -43456,7 +43456,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>4292.46</v>
+        <v>4357.81</v>
       </c>
     </row>
     <row r="706">
@@ -43517,7 +43517,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>57901.54</v>
+        <v>58783.03</v>
       </c>
     </row>
     <row r="707">
@@ -43578,7 +43578,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>74013.74000000001</v>
+        <v>75140.52</v>
       </c>
     </row>
     <row r="708">
@@ -43639,7 +43639,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>6808.28</v>
+        <v>6973.84</v>
       </c>
     </row>
     <row r="709">
@@ -43700,7 +43700,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>2023.64</v>
+        <v>2072.85</v>
       </c>
     </row>
     <row r="710">
@@ -43761,7 +43761,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>791.14</v>
+        <v>810.37</v>
       </c>
     </row>
     <row r="711">
@@ -43822,7 +43822,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>1966.38</v>
+        <v>2014.2</v>
       </c>
     </row>
     <row r="712">
@@ -43883,7 +43883,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>800.7</v>
+        <v>820.17</v>
       </c>
     </row>
     <row r="713">
@@ -43944,7 +43944,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>6916.37</v>
+        <v>7084.56</v>
       </c>
     </row>
     <row r="714">
@@ -44005,7 +44005,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>2373.36</v>
+        <v>2431.08</v>
       </c>
     </row>
     <row r="715">
@@ -44066,7 +44066,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>37674.9</v>
+        <v>38591.07</v>
       </c>
     </row>
     <row r="716">
@@ -44127,7 +44127,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>28661.67</v>
+        <v>29358.66</v>
       </c>
     </row>
     <row r="717">
@@ -44188,7 +44188,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>2827.87</v>
+        <v>2896.63</v>
       </c>
     </row>
     <row r="718">
@@ -44249,7 +44249,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>1801.89</v>
+        <v>1845.71</v>
       </c>
     </row>
     <row r="719">
@@ -44310,7 +44310,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>1984.98</v>
+        <v>2033.25</v>
       </c>
     </row>
     <row r="720">
@@ -44371,7 +44371,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>3288.61</v>
+        <v>3368.58</v>
       </c>
     </row>
     <row r="721">
@@ -44432,7 +44432,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>2480.57</v>
+        <v>2540.89</v>
       </c>
     </row>
     <row r="722">
@@ -44493,7 +44493,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>1063</v>
+        <v>1088.85</v>
       </c>
     </row>
     <row r="723">
@@ -44554,7 +44554,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>5303.58</v>
+        <v>5432.55</v>
       </c>
     </row>
     <row r="724">
@@ -44615,7 +44615,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>18792.41</v>
+        <v>19249.4</v>
       </c>
     </row>
     <row r="725">
@@ -44676,7 +44676,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>19490.99</v>
+        <v>19964.96</v>
       </c>
     </row>
     <row r="726">
@@ -44737,7 +44737,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>12328.69</v>
+        <v>12628.5</v>
       </c>
     </row>
     <row r="727">
@@ -44798,7 +44798,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>5128.62</v>
+        <v>5253.34</v>
       </c>
     </row>
     <row r="728">
@@ -44859,7 +44859,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>860.23</v>
+        <v>881.14</v>
       </c>
     </row>
     <row r="729">
@@ -44920,7 +44920,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>926.98</v>
+        <v>949.53</v>
       </c>
     </row>
     <row r="730">
@@ -44981,7 +44981,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>7929.79</v>
+        <v>8122.62</v>
       </c>
     </row>
     <row r="731">
@@ -45042,7 +45042,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>3939.14</v>
+        <v>4034.94</v>
       </c>
     </row>
     <row r="732">
@@ -45103,7 +45103,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>3150.14</v>
+        <v>3226.74</v>
       </c>
     </row>
     <row r="733">
@@ -45164,7 +45164,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>6940.06</v>
+        <v>7108.82</v>
       </c>
     </row>
     <row r="734">
@@ -45225,7 +45225,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>33230.42</v>
+        <v>34038.51</v>
       </c>
     </row>
     <row r="735">
@@ -45286,7 +45286,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>11402.33</v>
+        <v>11679.6</v>
       </c>
     </row>
     <row r="736">
@@ -45347,7 +45347,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>2916.82</v>
+        <v>2987.76</v>
       </c>
     </row>
     <row r="737">
@@ -45408,7 +45408,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>18922.75</v>
+        <v>19382.9</v>
       </c>
     </row>
     <row r="738">
@@ -45469,7 +45469,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>6539.46</v>
+        <v>6698.48</v>
       </c>
     </row>
     <row r="739">
@@ -45530,7 +45530,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>2087.25</v>
+        <v>2138.01</v>
       </c>
     </row>
     <row r="740">
@@ -45591,7 +45591,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>813.7</v>
+        <v>833.49</v>
       </c>
     </row>
     <row r="741">
@@ -45652,7 +45652,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>2392.03</v>
+        <v>2450.2</v>
       </c>
     </row>
     <row r="742">
@@ -45713,7 +45713,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>10812.39</v>
+        <v>11075.32</v>
       </c>
     </row>
     <row r="743">
@@ -45774,7 +45774,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>1923.05</v>
+        <v>1969.81</v>
       </c>
     </row>
     <row r="744">
@@ -45835,7 +45835,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>5655.65</v>
+        <v>5793.18</v>
       </c>
     </row>
     <row r="745">
@@ -45896,7 +45896,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>813.34</v>
+        <v>833.12</v>
       </c>
     </row>
     <row r="746">
@@ -45957,7 +45957,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>1333.51</v>
+        <v>1365.94</v>
       </c>
     </row>
     <row r="747">
@@ -46018,7 +46018,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>12954.88</v>
+        <v>13269.91</v>
       </c>
     </row>
     <row r="748">
@@ -46079,7 +46079,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>8992.66</v>
+        <v>9211.34</v>
       </c>
     </row>
     <row r="749">
@@ -46140,7 +46140,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>2827.69</v>
+        <v>2896.45</v>
       </c>
     </row>
     <row r="750">
@@ -46201,7 +46201,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>3912.95</v>
+        <v>4008.1</v>
       </c>
     </row>
     <row r="751">
@@ -46262,7 +46262,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>2474.57</v>
+        <v>2534.74</v>
       </c>
     </row>
     <row r="752">
@@ -46323,7 +46323,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>3065.44</v>
+        <v>3139.99</v>
       </c>
     </row>
     <row r="753">
@@ -46384,7 +46384,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>7910.21</v>
+        <v>8102.57</v>
       </c>
     </row>
     <row r="754">
@@ -46445,7 +46445,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>24191.32</v>
+        <v>24779.6</v>
       </c>
     </row>
     <row r="755">
@@ -46506,7 +46506,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>10109.4</v>
+        <v>10355.24</v>
       </c>
     </row>
     <row r="756">
@@ -46567,7 +46567,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>2863.19</v>
+        <v>2932.81</v>
       </c>
     </row>
     <row r="757">
@@ -46628,7 +46628,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>10618.9</v>
+        <v>10877.13</v>
       </c>
     </row>
     <row r="758">
@@ -46689,7 +46689,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>7865.04</v>
+        <v>8056.3</v>
       </c>
     </row>
     <row r="759">
@@ -46750,7 +46750,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>2543.14</v>
+        <v>2604.98</v>
       </c>
     </row>
     <row r="760">
@@ -46811,7 +46811,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>2290.11</v>
+        <v>2345.8</v>
       </c>
     </row>
     <row r="761">
@@ -46872,7 +46872,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>2081.91</v>
+        <v>2132.53</v>
       </c>
     </row>
     <row r="762">
@@ -46933,7 +46933,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>2260.55</v>
+        <v>2315.52</v>
       </c>
     </row>
     <row r="763">
@@ -46994,7 +46994,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>3499.46</v>
+        <v>3584.56</v>
       </c>
     </row>
     <row r="764">
@@ -47055,7 +47055,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>10047.14</v>
+        <v>10291.46</v>
       </c>
     </row>
     <row r="765">
@@ -47116,7 +47116,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>6554.68</v>
+        <v>6714.07</v>
       </c>
     </row>
     <row r="766">
@@ -47177,7 +47177,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>7801.14</v>
+        <v>7990.84</v>
       </c>
     </row>
     <row r="767">
@@ -47238,7 +47238,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>12894.97</v>
+        <v>13208.55</v>
       </c>
     </row>
     <row r="768">
@@ -47299,7 +47299,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>9241.440000000001</v>
+        <v>9466.17</v>
       </c>
     </row>
     <row r="769">
@@ -47360,7 +47360,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>8496.360000000001</v>
+        <v>8702.98</v>
       </c>
     </row>
     <row r="770">
@@ -47421,7 +47421,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>4495.62</v>
+        <v>4604.94</v>
       </c>
     </row>
     <row r="771">
@@ -47482,7 +47482,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>6443.62</v>
+        <v>6600.31</v>
       </c>
     </row>
     <row r="772">
@@ -47543,7 +47543,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>7631.53</v>
+        <v>7824.46</v>
       </c>
     </row>
     <row r="773">
@@ -47604,7 +47604,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>25881.9</v>
+        <v>26536.2</v>
       </c>
     </row>
     <row r="774">
@@ -47665,7 +47665,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>792.98</v>
+        <v>813.03</v>
       </c>
     </row>
     <row r="775">
@@ -47726,7 +47726,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>913.95</v>
+        <v>937.05</v>
       </c>
     </row>
     <row r="776">
@@ -47787,7 +47787,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>4012.77</v>
+        <v>4114.21</v>
       </c>
     </row>
     <row r="777">
@@ -47848,7 +47848,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>8066.87</v>
+        <v>8270.799999999999</v>
       </c>
     </row>
     <row r="778">
@@ -47909,7 +47909,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>3798.32</v>
+        <v>3894.34</v>
       </c>
     </row>
     <row r="779">
@@ -47970,7 +47970,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>1685.67</v>
+        <v>1728.28</v>
       </c>
     </row>
     <row r="780">
@@ -48031,7 +48031,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>6775.99</v>
+        <v>6947.29</v>
       </c>
     </row>
     <row r="781">
@@ -48092,7 +48092,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>7888.16</v>
+        <v>8087.57</v>
       </c>
     </row>
     <row r="782">
@@ -48153,7 +48153,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>2846.76</v>
+        <v>2918.73</v>
       </c>
     </row>
     <row r="783">
@@ -48214,7 +48214,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>2605.29</v>
+        <v>2671.15</v>
       </c>
     </row>
     <row r="784">
@@ -48275,7 +48275,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>4496.43</v>
+        <v>4610.1</v>
       </c>
     </row>
     <row r="785">
@@ -48336,7 +48336,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>800.42</v>
+        <v>820.66</v>
       </c>
     </row>
     <row r="786">
@@ -48397,7 +48397,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>6161.75</v>
+        <v>6317.52</v>
       </c>
     </row>
     <row r="787">
@@ -48458,7 +48458,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>4980.77</v>
+        <v>5106.69</v>
       </c>
     </row>
     <row r="788">
@@ -48519,7 +48519,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>1699.45</v>
+        <v>1742.41</v>
       </c>
     </row>
     <row r="789">
@@ -48580,7 +48580,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>2446.78</v>
+        <v>2508.64</v>
       </c>
     </row>
     <row r="790">
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>2855.3</v>
+        <v>2927.49</v>
       </c>
     </row>
     <row r="791">
@@ -48702,7 +48702,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>2129.46</v>
+        <v>2183.29</v>
       </c>
     </row>
     <row r="792">
@@ -48763,7 +48763,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>3638.93</v>
+        <v>3730.92</v>
       </c>
     </row>
     <row r="793">
@@ -48824,7 +48824,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>1846.34</v>
+        <v>1893.02</v>
       </c>
     </row>
     <row r="794">
@@ -48885,7 +48885,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>2593.52</v>
+        <v>2659.08</v>
       </c>
     </row>
     <row r="795">
@@ -48946,7 +48946,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>4067.03</v>
+        <v>4169.85</v>
       </c>
     </row>
     <row r="796">
@@ -49007,7 +49007,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>7846.57</v>
+        <v>8044.93</v>
       </c>
     </row>
     <row r="797">
@@ -49068,7 +49068,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>6804.87</v>
+        <v>6976.9</v>
       </c>
     </row>
     <row r="798">
@@ -49129,7 +49129,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>7869.87</v>
+        <v>8068.82</v>
       </c>
     </row>
     <row r="799">
@@ -49190,7 +49190,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>2082.58</v>
+        <v>2135.23</v>
       </c>
     </row>
     <row r="800">
@@ -49251,7 +49251,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>22607.14</v>
+        <v>23178.65</v>
       </c>
     </row>
     <row r="801">
@@ -49312,7 +49312,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>54824.24</v>
+        <v>56210.2</v>
       </c>
     </row>
     <row r="802">
@@ -49373,7 +49373,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>7302.99</v>
+        <v>7487.61</v>
       </c>
     </row>
     <row r="803">
@@ -49434,7 +49434,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>2296.36</v>
+        <v>2354.41</v>
       </c>
     </row>
     <row r="804">
@@ -49495,7 +49495,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>4041.92</v>
+        <v>4144.1</v>
       </c>
     </row>
     <row r="805">
@@ -49556,7 +49556,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>3654.61</v>
+        <v>3746.99</v>
       </c>
     </row>
     <row r="806">
@@ -49617,7 +49617,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>2002.06</v>
+        <v>2052.68</v>
       </c>
     </row>
     <row r="807">
@@ -49678,7 +49678,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>2640.02</v>
+        <v>2706.76</v>
       </c>
     </row>
     <row r="808">
@@ -49739,7 +49739,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>3604.52</v>
+        <v>3695.64</v>
       </c>
     </row>
     <row r="809">
@@ -49800,7 +49800,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>2369.28</v>
+        <v>2429.18</v>
       </c>
     </row>
     <row r="810">
@@ -49861,7 +49861,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>1856.3</v>
+        <v>1903.23</v>
       </c>
     </row>
     <row r="811">
@@ -49922,7 +49922,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>2064</v>
+        <v>2116.18</v>
       </c>
     </row>
     <row r="812">
@@ -49983,7 +49983,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>5206.67</v>
+        <v>5338.29</v>
       </c>
     </row>
     <row r="813">
@@ -50044,7 +50044,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>4894.4</v>
+        <v>5018.13</v>
       </c>
     </row>
     <row r="814">
@@ -50105,7 +50105,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>2579.57</v>
+        <v>2644.78</v>
       </c>
     </row>
     <row r="815">
@@ -50166,7 +50166,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>2587.08</v>
+        <v>2652.48</v>
       </c>
     </row>
     <row r="816">
@@ -50227,7 +50227,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>2410.2</v>
+        <v>2471.13</v>
       </c>
     </row>
     <row r="817">
@@ -50288,7 +50288,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>2010.59</v>
+        <v>2061.41</v>
       </c>
     </row>
     <row r="818">
@@ -50349,7 +50349,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>2408.91</v>
+        <v>2481.95</v>
       </c>
     </row>
     <row r="819">
@@ -50410,7 +50410,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>17647.83</v>
+        <v>18182.96</v>
       </c>
     </row>
     <row r="820">
@@ -50471,7 +50471,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>4030.26</v>
+        <v>4152.47</v>
       </c>
     </row>
     <row r="821">
@@ -50532,7 +50532,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>7785.61</v>
+        <v>8021.7</v>
       </c>
     </row>
     <row r="822">
@@ -50593,7 +50593,7 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>4103.53</v>
+        <v>4227.96</v>
       </c>
     </row>
     <row r="823">
@@ -50654,7 +50654,7 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>27117.26</v>
+        <v>27939.54</v>
       </c>
     </row>
     <row r="824">
@@ -50715,7 +50715,7 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>7495.38</v>
+        <v>7722.66</v>
       </c>
     </row>
     <row r="825">
@@ -50776,7 +50776,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>8089.08</v>
+        <v>8334.370000000001</v>
       </c>
     </row>
     <row r="826">
@@ -50837,7 +50837,7 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>2782.62</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="827">
@@ -50898,7 +50898,7 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>817.8200000000001</v>
+        <v>842.62</v>
       </c>
     </row>
     <row r="828">
@@ -50959,7 +50959,7 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>1169.5</v>
+        <v>1204.97</v>
       </c>
     </row>
     <row r="829">
@@ -51020,7 +51020,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>7879.94</v>
+        <v>8118.88</v>
       </c>
     </row>
     <row r="830">
@@ -51081,7 +51081,7 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>5298.67</v>
+        <v>5459.34</v>
       </c>
     </row>
     <row r="831">
@@ -51142,7 +51142,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>7003.37</v>
+        <v>7215.74</v>
       </c>
     </row>
     <row r="832">
@@ -51203,7 +51203,7 @@
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>7584.53</v>
+        <v>7814.51</v>
       </c>
     </row>
     <row r="833">
@@ -51264,7 +51264,7 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>12350.1</v>
+        <v>12724.59</v>
       </c>
     </row>
     <row r="834">
@@ -51325,7 +51325,7 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>828.89</v>
+        <v>854.02</v>
       </c>
     </row>
     <row r="835">
@@ -51386,7 +51386,7 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>2823.63</v>
+        <v>2909.26</v>
       </c>
     </row>
     <row r="836">
@@ -51447,7 +51447,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>32954.05</v>
+        <v>33953.32</v>
       </c>
     </row>
     <row r="837">
@@ -51508,7 +51508,7 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>4014.39</v>
+        <v>4136.12</v>
       </c>
     </row>
     <row r="838">
@@ -51569,7 +51569,7 @@
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>9479.440000000001</v>
+        <v>9766.889999999999</v>
       </c>
     </row>
     <row r="839">
@@ -51630,7 +51630,7 @@
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>5933.71</v>
+        <v>6113.64</v>
       </c>
     </row>
     <row r="840">
@@ -51691,7 +51691,7 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>2444</v>
+        <v>2518.11</v>
       </c>
     </row>
     <row r="841">
@@ -51752,7 +51752,7 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>1851.24</v>
+        <v>1907.37</v>
       </c>
     </row>
     <row r="842">
@@ -51813,7 +51813,7 @@
         </is>
       </c>
       <c r="M842" s="2" t="n">
-        <v>6771.66</v>
+        <v>6977</v>
       </c>
     </row>
     <row r="843">
@@ -51874,7 +51874,7 @@
         </is>
       </c>
       <c r="M843" s="2" t="n">
-        <v>839.71</v>
+        <v>865.17</v>
       </c>
     </row>
     <row r="844">
@@ -51935,7 +51935,7 @@
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>2266.51</v>
+        <v>2335.24</v>
       </c>
     </row>
     <row r="845">
@@ -51996,7 +51996,7 @@
         </is>
       </c>
       <c r="M845" s="2" t="n">
-        <v>5766.76</v>
+        <v>5941.63</v>
       </c>
     </row>
     <row r="846">
@@ -52057,7 +52057,7 @@
         </is>
       </c>
       <c r="M846" s="2" t="n">
-        <v>2252.2</v>
+        <v>2320.5</v>
       </c>
     </row>
     <row r="847">
@@ -52118,7 +52118,7 @@
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>2756.87</v>
+        <v>2840.47</v>
       </c>
     </row>
     <row r="848">
@@ -52179,7 +52179,7 @@
         </is>
       </c>
       <c r="M848" s="2" t="n">
-        <v>3749.91</v>
+        <v>3863.62</v>
       </c>
     </row>
     <row r="849">
@@ -52240,7 +52240,7 @@
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>2438.57</v>
+        <v>2512.51</v>
       </c>
     </row>
     <row r="850">
@@ -52301,7 +52301,7 @@
         </is>
       </c>
       <c r="M850" s="2" t="n">
-        <v>2837.8</v>
+        <v>2923.85</v>
       </c>
     </row>
     <row r="851">
@@ -52362,7 +52362,7 @@
         </is>
       </c>
       <c r="M851" s="2" t="n">
-        <v>792.12</v>
+        <v>816.14</v>
       </c>
     </row>
     <row r="852">
@@ -52423,7 +52423,7 @@
         </is>
       </c>
       <c r="M852" s="2" t="n">
-        <v>43384.85</v>
+        <v>44700.41</v>
       </c>
     </row>
     <row r="853">
@@ -52484,7 +52484,7 @@
         </is>
       </c>
       <c r="M853" s="2" t="n">
-        <v>4372.48</v>
+        <v>4505.06</v>
       </c>
     </row>
     <row r="854">
@@ -52545,7 +52545,7 @@
         </is>
       </c>
       <c r="M854" s="2" t="n">
-        <v>25607.53</v>
+        <v>26384.03</v>
       </c>
     </row>
     <row r="855">
@@ -52606,7 +52606,7 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>2687.94</v>
+        <v>2769.45</v>
       </c>
     </row>
     <row r="856">
@@ -52667,7 +52667,7 @@
         </is>
       </c>
       <c r="M856" s="2" t="n">
-        <v>78343.10000000001</v>
+        <v>80718.7</v>
       </c>
     </row>
     <row r="857">
@@ -52728,7 +52728,7 @@
         </is>
       </c>
       <c r="M857" s="2" t="n">
-        <v>2236.06</v>
+        <v>2303.86</v>
       </c>
     </row>
     <row r="858">
@@ -52789,7 +52789,7 @@
         </is>
       </c>
       <c r="M858" s="2" t="n">
-        <v>19675.46</v>
+        <v>20272.08</v>
       </c>
     </row>
     <row r="859">
@@ -52850,7 +52850,7 @@
         </is>
       </c>
       <c r="M859" s="2" t="n">
-        <v>16278.54</v>
+        <v>16772.16</v>
       </c>
     </row>
     <row r="860">
@@ -52911,7 +52911,7 @@
         </is>
       </c>
       <c r="M860" s="2" t="n">
-        <v>6945.8</v>
+        <v>7156.42</v>
       </c>
     </row>
     <row r="861">
@@ -52972,7 +52972,7 @@
         </is>
       </c>
       <c r="M861" s="2" t="n">
-        <v>3096.81</v>
+        <v>3190.72</v>
       </c>
     </row>
     <row r="862">
@@ -53033,7 +53033,7 @@
         </is>
       </c>
       <c r="M862" s="2" t="n">
-        <v>8262.41</v>
+        <v>8512.950000000001</v>
       </c>
     </row>
     <row r="863">
@@ -53094,7 +53094,7 @@
         </is>
       </c>
       <c r="M863" s="2" t="n">
-        <v>2146.09</v>
+        <v>2211.17</v>
       </c>
     </row>
     <row r="864">
@@ -53155,7 +53155,7 @@
         </is>
       </c>
       <c r="M864" s="2" t="n">
-        <v>18055.98</v>
+        <v>18603.49</v>
       </c>
     </row>
     <row r="865">
@@ -53216,7 +53216,7 @@
         </is>
       </c>
       <c r="M865" s="2" t="n">
-        <v>10377.63</v>
+        <v>10692.32</v>
       </c>
     </row>
     <row r="866">
@@ -53277,7 +53277,7 @@
         </is>
       </c>
       <c r="M866" s="2" t="n">
-        <v>13097.24</v>
+        <v>13494.39</v>
       </c>
     </row>
     <row r="867">
@@ -53338,7 +53338,7 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>10226.55</v>
+        <v>10536.65</v>
       </c>
     </row>
     <row r="868">
@@ -53399,7 +53399,7 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>18083.22</v>
+        <v>18631.56</v>
       </c>
     </row>
     <row r="869">
@@ -53460,7 +53460,7 @@
         </is>
       </c>
       <c r="M869" s="2" t="n">
-        <v>6782.72</v>
+        <v>6988.4</v>
       </c>
     </row>
     <row r="870">
@@ -53521,7 +53521,7 @@
         </is>
       </c>
       <c r="M870" s="2" t="n">
-        <v>11130.43</v>
+        <v>11467.94</v>
       </c>
     </row>
     <row r="871">
@@ -53582,7 +53582,7 @@
         </is>
       </c>
       <c r="M871" s="2" t="n">
-        <v>39568.46</v>
+        <v>40768.29</v>
       </c>
     </row>
     <row r="872">
@@ -53643,7 +53643,7 @@
         </is>
       </c>
       <c r="M872" s="2" t="n">
-        <v>3794.33</v>
+        <v>3909.38</v>
       </c>
     </row>
     <row r="873">
@@ -53704,7 +53704,7 @@
         </is>
       </c>
       <c r="M873" s="2" t="n">
-        <v>9163.67</v>
+        <v>9441.540000000001</v>
       </c>
     </row>
     <row r="874">
@@ -53765,7 +53765,7 @@
         </is>
       </c>
       <c r="M874" s="2" t="n">
-        <v>7914.18</v>
+        <v>8154.17</v>
       </c>
     </row>
     <row r="875">
@@ -53826,7 +53826,7 @@
         </is>
       </c>
       <c r="M875" s="2" t="n">
-        <v>3108.26</v>
+        <v>3202.51</v>
       </c>
     </row>
     <row r="876">
@@ -53887,7 +53887,7 @@
         </is>
       </c>
       <c r="M876" s="2" t="n">
-        <v>2338.09</v>
+        <v>2408.99</v>
       </c>
     </row>
     <row r="877">
@@ -53948,7 +53948,7 @@
         </is>
       </c>
       <c r="M877" s="2" t="n">
-        <v>11357.17</v>
+        <v>11701.56</v>
       </c>
     </row>
     <row r="878">
@@ -54009,7 +54009,7 @@
         </is>
       </c>
       <c r="M878" s="2" t="n">
-        <v>2728.04</v>
+        <v>2810.77</v>
       </c>
     </row>
     <row r="879">
@@ -54070,7 +54070,7 @@
         </is>
       </c>
       <c r="M879" s="2" t="n">
-        <v>2465.82</v>
+        <v>2540.59</v>
       </c>
     </row>
     <row r="880">
@@ -54131,7 +54131,7 @@
         </is>
       </c>
       <c r="M880" s="2" t="n">
-        <v>3651.35</v>
+        <v>3762.07</v>
       </c>
     </row>
     <row r="881">
@@ -54192,7 +54192,7 @@
         </is>
       </c>
       <c r="M881" s="2" t="n">
-        <v>1048.16</v>
+        <v>1079.94</v>
       </c>
     </row>
     <row r="882">
@@ -54253,7 +54253,7 @@
         </is>
       </c>
       <c r="M882" s="2" t="n">
-        <v>9896.67</v>
+        <v>10196.77</v>
       </c>
     </row>
     <row r="883">
@@ -54314,7 +54314,7 @@
         </is>
       </c>
       <c r="M883" s="2" t="n">
-        <v>6245.48</v>
+        <v>6434.86</v>
       </c>
     </row>
     <row r="884">
@@ -54375,7 +54375,7 @@
         </is>
       </c>
       <c r="M884" s="2" t="n">
-        <v>3115.26</v>
+        <v>3209.72</v>
       </c>
     </row>
     <row r="885">
@@ -54436,7 +54436,7 @@
         </is>
       </c>
       <c r="M885" s="2" t="n">
-        <v>1650.95</v>
+        <v>1701.01</v>
       </c>
     </row>
     <row r="886">
@@ -54497,7 +54497,7 @@
         </is>
       </c>
       <c r="M886" s="2" t="n">
-        <v>12453.54</v>
+        <v>12831.17</v>
       </c>
     </row>
     <row r="887">
@@ -54558,7 +54558,7 @@
         </is>
       </c>
       <c r="M887" s="2" t="n">
-        <v>3913.75</v>
+        <v>4032.43</v>
       </c>
     </row>
     <row r="888">
@@ -54619,7 +54619,7 @@
         </is>
       </c>
       <c r="M888" s="2" t="n">
-        <v>1860.19</v>
+        <v>1916.59</v>
       </c>
     </row>
     <row r="889">
@@ -54680,7 +54680,7 @@
         </is>
       </c>
       <c r="M889" s="2" t="n">
-        <v>11463.99</v>
+        <v>11811.62</v>
       </c>
     </row>
     <row r="890">
@@ -54741,7 +54741,7 @@
         </is>
       </c>
       <c r="M890" s="2" t="n">
-        <v>1597.78</v>
+        <v>1646.23</v>
       </c>
     </row>
     <row r="891">
@@ -54802,7 +54802,7 @@
         </is>
       </c>
       <c r="M891" s="2" t="n">
-        <v>6741.4</v>
+        <v>6945.82</v>
       </c>
     </row>
     <row r="892">
@@ -54863,7 +54863,7 @@
         </is>
       </c>
       <c r="M892" s="2" t="n">
-        <v>67806.73</v>
+        <v>69822.14999999999</v>
       </c>
     </row>
     <row r="893">
@@ -54924,7 +54924,7 @@
         </is>
       </c>
       <c r="M893" s="2" t="n">
-        <v>1696.76</v>
+        <v>1747.19</v>
       </c>
     </row>
     <row r="894">
@@ -54985,7 +54985,7 @@
         </is>
       </c>
       <c r="M894" s="2" t="n">
-        <v>5703.75</v>
+        <v>5873.29</v>
       </c>
     </row>
     <row r="895">
@@ -55046,7 +55046,7 @@
         </is>
       </c>
       <c r="M895" s="2" t="n">
-        <v>8357.049999999999</v>
+        <v>8605.440000000001</v>
       </c>
     </row>
     <row r="896">
@@ -55107,7 +55107,7 @@
         </is>
       </c>
       <c r="M896" s="2" t="n">
-        <v>10155.51</v>
+        <v>10457.36</v>
       </c>
     </row>
     <row r="897">
@@ -55168,7 +55168,7 @@
         </is>
       </c>
       <c r="M897" s="2" t="n">
-        <v>3807.55</v>
+        <v>3920.72</v>
       </c>
     </row>
     <row r="898">
@@ -55229,7 +55229,7 @@
         </is>
       </c>
       <c r="M898" s="2" t="n">
-        <v>2985.14</v>
+        <v>3073.87</v>
       </c>
     </row>
     <row r="899">
@@ -55290,7 +55290,7 @@
         </is>
       </c>
       <c r="M899" s="2" t="n">
-        <v>1328.76</v>
+        <v>1368.26</v>
       </c>
     </row>
     <row r="900">
@@ -55351,7 +55351,7 @@
         </is>
       </c>
       <c r="M900" s="2" t="n">
-        <v>2722.82</v>
+        <v>2803.75</v>
       </c>
     </row>
     <row r="901">
@@ -55412,7 +55412,7 @@
         </is>
       </c>
       <c r="M901" s="2" t="n">
-        <v>2935.72</v>
+        <v>3022.97</v>
       </c>
     </row>
     <row r="902">
@@ -55473,7 +55473,7 @@
         </is>
       </c>
       <c r="M902" s="2" t="n">
-        <v>16659.97</v>
+        <v>17155.16</v>
       </c>
     </row>
     <row r="903">
@@ -55534,7 +55534,7 @@
         </is>
       </c>
       <c r="M903" s="2" t="n">
-        <v>3473.86</v>
+        <v>3577.11</v>
       </c>
     </row>
     <row r="904">
@@ -55595,7 +55595,7 @@
         </is>
       </c>
       <c r="M904" s="2" t="n">
-        <v>2545.27</v>
+        <v>2620.92</v>
       </c>
     </row>
     <row r="905">
@@ -55656,7 +55656,7 @@
         </is>
       </c>
       <c r="M905" s="2" t="n">
-        <v>2489.81</v>
+        <v>2563.81</v>
       </c>
     </row>
     <row r="906">
@@ -55717,7 +55717,7 @@
         </is>
       </c>
       <c r="M906" s="2" t="n">
-        <v>19939.3</v>
+        <v>20531.95</v>
       </c>
     </row>
     <row r="907">
@@ -55778,7 +55778,7 @@
         </is>
       </c>
       <c r="M907" s="2" t="n">
-        <v>26155.38</v>
+        <v>26932.8</v>
       </c>
     </row>
     <row r="908">
@@ -55839,7 +55839,7 @@
         </is>
       </c>
       <c r="M908" s="2" t="n">
-        <v>1076.96</v>
+        <v>1108.98</v>
       </c>
     </row>
     <row r="909">
@@ -55900,7 +55900,7 @@
         </is>
       </c>
       <c r="M909" s="2" t="n">
-        <v>8786.43</v>
+        <v>9047.59</v>
       </c>
     </row>
     <row r="910">
@@ -55961,7 +55961,7 @@
         </is>
       </c>
       <c r="M910" s="2" t="n">
-        <v>1859.78</v>
+        <v>1915.06</v>
       </c>
     </row>
     <row r="911">
@@ -56022,7 +56022,7 @@
         </is>
       </c>
       <c r="M911" s="2" t="n">
-        <v>3874.02</v>
+        <v>3989.17</v>
       </c>
     </row>
     <row r="912">
@@ -56083,7 +56083,7 @@
         </is>
       </c>
       <c r="M912" s="2" t="n">
-        <v>9636.4</v>
+        <v>9922.82</v>
       </c>
     </row>
     <row r="913">
@@ -56144,7 +56144,7 @@
         </is>
       </c>
       <c r="M913" s="2" t="n">
-        <v>8154.17</v>
+        <v>8396.540000000001</v>
       </c>
     </row>
     <row r="914">
@@ -56205,7 +56205,7 @@
         </is>
       </c>
       <c r="M914" s="2" t="n">
-        <v>3914.77</v>
+        <v>4031.13</v>
       </c>
     </row>
     <row r="915">
@@ -56266,7 +56266,7 @@
         </is>
       </c>
       <c r="M915" s="2" t="n">
-        <v>922.04</v>
+        <v>949.45</v>
       </c>
     </row>
     <row r="916">
@@ -56327,7 +56327,7 @@
         </is>
       </c>
       <c r="M916" s="2" t="n">
-        <v>3619.68</v>
+        <v>3727.27</v>
       </c>
     </row>
     <row r="917">
@@ -56388,7 +56388,7 @@
         </is>
       </c>
       <c r="M917" s="2" t="n">
-        <v>6309.94</v>
+        <v>6497.49</v>
       </c>
     </row>
     <row r="918">
@@ -56449,7 +56449,7 @@
         </is>
       </c>
       <c r="M918" s="2" t="n">
-        <v>2158</v>
+        <v>2222.14</v>
       </c>
     </row>
     <row r="919">
@@ -56510,7 +56510,7 @@
         </is>
       </c>
       <c r="M919" s="2" t="n">
-        <v>2181.2</v>
+        <v>2246.03</v>
       </c>
     </row>
     <row r="920">
@@ -56571,7 +56571,7 @@
         </is>
       </c>
       <c r="M920" s="2" t="n">
-        <v>3267.81</v>
+        <v>3364.94</v>
       </c>
     </row>
     <row r="921">
@@ -56632,7 +56632,7 @@
         </is>
       </c>
       <c r="M921" s="2" t="n">
-        <v>6667.09</v>
+        <v>6865.25</v>
       </c>
     </row>
     <row r="922">
@@ -56693,7 +56693,7 @@
         </is>
       </c>
       <c r="M922" s="2" t="n">
-        <v>49331.72</v>
+        <v>50798.01</v>
       </c>
     </row>
     <row r="923">
@@ -56754,7 +56754,7 @@
         </is>
       </c>
       <c r="M923" s="2" t="n">
-        <v>4892.11</v>
+        <v>5037.52</v>
       </c>
     </row>
     <row r="924">
@@ -56815,7 +56815,7 @@
         </is>
       </c>
       <c r="M924" s="2" t="n">
-        <v>10087.15</v>
+        <v>10386.97</v>
       </c>
     </row>
     <row r="925">
@@ -56876,7 +56876,7 @@
         </is>
       </c>
       <c r="M925" s="2" t="n">
-        <v>8596</v>
+        <v>8851.5</v>
       </c>
     </row>
     <row r="926">
@@ -56937,7 +56937,7 @@
         </is>
       </c>
       <c r="M926" s="2" t="n">
-        <v>38152.02</v>
+        <v>39286.01</v>
       </c>
     </row>
     <row r="927">
@@ -56998,7 +56998,7 @@
         </is>
       </c>
       <c r="M927" s="2" t="n">
-        <v>11097.54</v>
+        <v>11427.4</v>
       </c>
     </row>
     <row r="928">
@@ -57059,7 +57059,7 @@
         </is>
       </c>
       <c r="M928" s="2" t="n">
-        <v>3581.99</v>
+        <v>3688.45</v>
       </c>
     </row>
     <row r="929">
@@ -57120,7 +57120,7 @@
         </is>
       </c>
       <c r="M929" s="2" t="n">
-        <v>3362.42</v>
+        <v>3462.36</v>
       </c>
     </row>
     <row r="930">
@@ -57181,7 +57181,7 @@
         </is>
       </c>
       <c r="M930" s="2" t="n">
-        <v>3212.86</v>
+        <v>3308.35</v>
       </c>
     </row>
     <row r="931">
@@ -57242,7 +57242,7 @@
         </is>
       </c>
       <c r="M931" s="2" t="n">
-        <v>9592.530000000001</v>
+        <v>9877.639999999999</v>
       </c>
     </row>
     <row r="932">
@@ -57303,7 +57303,7 @@
         </is>
       </c>
       <c r="M932" s="2" t="n">
-        <v>3054.32</v>
+        <v>3145.1</v>
       </c>
     </row>
     <row r="933">
@@ -57364,7 +57364,7 @@
         </is>
       </c>
       <c r="M933" s="2" t="n">
-        <v>1357.28</v>
+        <v>1397.62</v>
       </c>
     </row>
     <row r="934">
@@ -57425,7 +57425,7 @@
         </is>
       </c>
       <c r="M934" s="2" t="n">
-        <v>2614.15</v>
+        <v>2691.85</v>
       </c>
     </row>
     <row r="935">
@@ -57486,7 +57486,7 @@
         </is>
       </c>
       <c r="M935" s="2" t="n">
-        <v>5641.81</v>
+        <v>5809.5</v>
       </c>
     </row>
     <row r="936">
@@ -57547,7 +57547,7 @@
         </is>
       </c>
       <c r="M936" s="2" t="n">
-        <v>3912.65</v>
+        <v>4028.95</v>
       </c>
     </row>
     <row r="937">
@@ -57608,7 +57608,7 @@
         </is>
       </c>
       <c r="M937" s="2" t="n">
-        <v>8496.27</v>
+        <v>8748.799999999999</v>
       </c>
     </row>
     <row r="938">
@@ -57669,7 +57669,7 @@
         </is>
       </c>
       <c r="M938" s="2" t="n">
-        <v>9037.459999999999</v>
+        <v>9306.08</v>
       </c>
     </row>
     <row r="939">
@@ -57730,7 +57730,7 @@
         </is>
       </c>
       <c r="M939" s="2" t="n">
-        <v>802.27</v>
+        <v>826.12</v>
       </c>
     </row>
     <row r="940">
@@ -57791,7 +57791,7 @@
         </is>
       </c>
       <c r="M940" s="2" t="n">
-        <v>14397.54</v>
+        <v>14825.48</v>
       </c>
     </row>
     <row r="941">
@@ -57852,7 +57852,7 @@
         </is>
       </c>
       <c r="M941" s="2" t="n">
-        <v>19739.05</v>
+        <v>20325.75</v>
       </c>
     </row>
     <row r="942">
@@ -57913,7 +57913,7 @@
         </is>
       </c>
       <c r="M942" s="2" t="n">
-        <v>2366.46</v>
+        <v>2436.79</v>
       </c>
     </row>
     <row r="943">
@@ -57974,7 +57974,7 @@
         </is>
       </c>
       <c r="M943" s="2" t="n">
-        <v>2884.06</v>
+        <v>2969.78</v>
       </c>
     </row>
     <row r="944">
@@ -58035,7 +58035,7 @@
         </is>
       </c>
       <c r="M944" s="2" t="n">
-        <v>3906.68</v>
+        <v>4022.79</v>
       </c>
     </row>
     <row r="945">
@@ -58096,7 +58096,7 @@
         </is>
       </c>
       <c r="M945" s="2" t="n">
-        <v>2889.53</v>
+        <v>2975.41</v>
       </c>
     </row>
     <row r="946">
@@ -58157,7 +58157,7 @@
         </is>
       </c>
       <c r="M946" s="2" t="n">
-        <v>878.26</v>
+        <v>904.37</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25563,7 +25563,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26173,7 +26173,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26722,7 +26722,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26783,7 +26783,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -27027,7 +27027,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27149,7 +27149,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28979,7 +28979,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29284,7 +29284,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -30138,7 +30138,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -32090,7 +32090,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32151,7 +32151,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32395,7 +32395,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32761,7 +32761,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32944,7 +32944,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33432,7 +33432,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34347,7 +34347,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34408,7 +34408,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -35262,7 +35262,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35567,7 +35567,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35628,7 +35628,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35750,7 +35750,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -36055,7 +36055,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36726,7 +36726,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36970,7 +36970,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37031,7 +37031,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37641,7 +37641,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -38068,7 +38068,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38312,7 +38312,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -39105,7 +39105,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39349,7 +39349,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39410,7 +39410,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -40813,7 +40813,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -41179,7 +41179,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41423,7 +41423,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41484,7 +41484,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41545,7 +41545,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41789,7 +41789,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -44839,7 +44839,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -44900,7 +44900,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -45266,7 +45266,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45876,7 +45876,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -47096,7 +47096,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -47279,7 +47279,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -47462,7 +47462,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -47828,7 +47828,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -48011,7 +48011,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
@@ -48682,7 +48682,7 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -48865,7 +48865,7 @@
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -49231,7 +49231,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -49536,7 +49536,7 @@
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -49780,7 +49780,7 @@
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -49841,7 +49841,7 @@
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -50085,7 +50085,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -50146,7 +50146,7 @@
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -50451,7 +50451,7 @@
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
@@ -51610,7 +51610,7 @@
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I839" t="inlineStr">
@@ -51854,7 +51854,7 @@
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -51915,7 +51915,7 @@
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
@@ -51976,7 +51976,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -52220,7 +52220,7 @@
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I849" t="inlineStr">
@@ -52647,7 +52647,7 @@
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
@@ -52952,7 +52952,7 @@
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
@@ -53074,7 +53074,7 @@
       </c>
       <c r="H863" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I863" t="inlineStr">
@@ -53684,7 +53684,7 @@
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
@@ -54111,7 +54111,7 @@
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
@@ -54355,7 +54355,7 @@
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I884" t="inlineStr">
@@ -54538,7 +54538,7 @@
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I887" t="inlineStr">
@@ -55026,7 +55026,7 @@
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
@@ -55209,7 +55209,7 @@
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I898" t="inlineStr">
@@ -55392,7 +55392,7 @@
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
@@ -55758,7 +55758,7 @@
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
@@ -56002,7 +56002,7 @@
       </c>
       <c r="H911" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I911" t="inlineStr">
@@ -56307,7 +56307,7 @@
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
@@ -56673,7 +56673,7 @@
       </c>
       <c r="H922" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
@@ -56734,7 +56734,7 @@
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
@@ -56795,7 +56795,7 @@
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I924" t="inlineStr">
@@ -56856,7 +56856,7 @@
       </c>
       <c r="H925" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I925" t="inlineStr">
@@ -57405,7 +57405,7 @@
       </c>
       <c r="H934" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I934" t="inlineStr">
@@ -57527,7 +57527,7 @@
       </c>
       <c r="H936" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I936" t="inlineStr">
@@ -57832,7 +57832,7 @@
       </c>
       <c r="H941" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I941" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M946"/>
+  <dimension ref="A1:M949"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Instituto Nacional de Neurocirugía</t>
+          <t>Instituto de Neurocirugía</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I.Municipalidad de San Pablo -Salud</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Río Negro - Salud</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE PENALOLEN</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>CORPORACIÓN SOCIAL Y CULTURAL DE CONCEPCIÓN-SEMCO</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>IMPRENTA DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NEGRETE DEPARTAMENTO COMUNAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE MARINA HOSP NAVAL ALMIR</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>ESCUELA DE GRUMETES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>ESCUELA DE GRUMETES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14812,7 +14812,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -14822,7 +14822,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14944,7 +14944,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION VI REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -15737,17 +15737,17 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>BASTIAN IGNACIO</t>
+          <t>Bastian Ignacio</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -15808,7 +15808,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16042,12 +16042,12 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16662,7 +16662,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -16703,7 +16703,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17638,7 +17638,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -17872,7 +17872,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18370,7 +18370,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -18553,7 +18553,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19407,7 +19407,7 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
@@ -19458,7 +19458,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20444,7 +20444,7 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
@@ -20861,7 +20861,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20973,7 +20973,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -21227,7 +21227,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
@@ -21959,7 +21959,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO SALUD MUNICIPALIDAD DE QUILLON</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22203,7 +22203,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -22325,7 +22325,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22518,7 +22518,7 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA PESCA ARTESANAL Y A</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23179,7 +23179,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23301,7 +23301,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23362,7 +23362,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Corporación del Deporte e Inclusión Social de la I</t>
+          <t>Corporación del Deporte e Inclusión Social de la Ilustre Municipalidad de Cerro Navia</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
@@ -23728,7 +23728,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -23799,7 +23799,7 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE AYSEN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24155,12 +24155,12 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -24521,7 +24521,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -24643,7 +24643,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -24704,7 +24704,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
@@ -25019,7 +25019,7 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Centro de Sangre y Tejidos de Concepcion</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -25690,7 +25690,7 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -25873,7 +25873,7 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>Comercial y distribuidora Centella Limitada</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NEGRETE DEPARTAMENTO COMUNAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -26666,7 +26666,7 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
@@ -26778,7 +26778,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27276,7 +27276,7 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -27388,7 +27388,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales IX Región</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -27632,7 +27632,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -27815,7 +27815,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NEGRETE DEPARTAMENTO COMUNAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -28151,7 +28151,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>1075952-6-CM26</t>
+          <t>1426095-5-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -28176,27 +28176,27 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>62.000.580-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Superintendencia de Educación Superior</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K455" t="inlineStr"/>
@@ -28206,7 +28206,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2689.76</v>
+        <v>1659.23</v>
       </c>
     </row>
     <row r="456">
@@ -28273,7 +28273,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>1426095-5-CM26</t>
+          <t>1075952-6-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -28298,27 +28298,27 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.580-0</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Superintendencia de Educación Superior</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K457" t="inlineStr"/>
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>1659.23</v>
+        <v>2689.76</v>
       </c>
     </row>
     <row r="458">
@@ -28425,7 +28425,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -28486,7 +28486,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -28852,7 +28852,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA LOS ANDES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -28974,7 +28974,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>DIRECCION DE RECUPERACION DE UNIDADES DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>3153-4-CM26</t>
+          <t>4559-15-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -29213,27 +29213,27 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>69.160.402-0</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K472" t="inlineStr"/>
@@ -29243,13 +29243,13 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>15928.69</v>
+        <v>3974.51</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>4559-15-CM26</t>
+          <t>3153-4-CM26</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -29274,27 +29274,27 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>69.160.402-0</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K473" t="inlineStr"/>
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>3974.51</v>
+        <v>15928.69</v>
       </c>
     </row>
     <row r="474">
@@ -29472,7 +29472,7 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
@@ -29523,7 +29523,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -29584,7 +29584,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -29645,7 +29645,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>Departamento de Salud Parral</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -29828,7 +29828,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -29960,7 +29960,7 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -30194,7 +30194,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>Departamento de Salud Parral</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -31048,7 +31048,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -31058,7 +31058,7 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
@@ -31170,7 +31170,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>CENTRAL ODONTOLOGICA PRIMERA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
@@ -31597,7 +31597,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -31607,7 +31607,7 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
@@ -31719,7 +31719,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -31780,12 +31780,12 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31841,12 +31841,12 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31963,7 +31963,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -32156,7 +32156,7 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
@@ -32207,7 +32207,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>Instituto Nacional de Neurocirugía</t>
+          <t>Instituto de Neurocirugía</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -32390,7 +32390,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -32461,7 +32461,7 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -32817,7 +32817,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -33000,7 +33000,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -33071,7 +33071,7 @@
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
@@ -33122,7 +33122,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -33132,7 +33132,7 @@
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
@@ -33488,7 +33488,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -33803,7 +33803,7 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDUARDO ANDRES </t>
+          <t xml:space="preserve">Eduardo Andres </t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
@@ -34098,7 +34098,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -34281,7 +34281,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -34342,7 +34342,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -34403,7 +34403,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -34464,7 +34464,7 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -34474,7 +34474,7 @@
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
@@ -34840,7 +34840,7 @@
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
@@ -34962,7 +34962,7 @@
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J566" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
@@ -35196,7 +35196,7 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>DIVISIÓN DE BIENESTAR SOCIAL</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -35206,7 +35206,7 @@
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
@@ -35257,7 +35257,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -35562,7 +35562,7 @@
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NEGRETE DEPARTAMENTO COMUNAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -35755,7 +35755,7 @@
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J579" t="inlineStr">
@@ -35806,7 +35806,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -35816,7 +35816,7 @@
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J580" t="inlineStr">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J587" t="inlineStr">
@@ -36416,7 +36416,7 @@
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J590" t="inlineStr">
@@ -36660,7 +36660,7 @@
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -36853,7 +36853,7 @@
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
@@ -36914,7 +36914,7 @@
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
@@ -37209,7 +37209,7 @@
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Tribunal de Juicio Oral en lo Penal de Copiapo</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
@@ -37463,7 +37463,7 @@
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
@@ -38063,7 +38063,7 @@
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -38124,7 +38124,7 @@
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>Superintendencia de Servicios Sanitarios</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -38612,7 +38612,7 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -38678,7 +38678,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38856,7 +38856,7 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE VALPARAISO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -39100,7 +39100,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE TALCAHUANO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -39161,7 +39161,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -39283,7 +39283,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -39527,7 +39527,7 @@
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -39659,7 +39659,7 @@
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
@@ -39776,7 +39776,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -40076,7 +40076,7 @@
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -40137,7 +40137,7 @@
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
@@ -40198,7 +40198,7 @@
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -40320,7 +40320,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Gendarmería</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -40452,7 +40452,7 @@
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
@@ -40574,7 +40574,7 @@
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
@@ -40635,7 +40635,7 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
@@ -40696,7 +40696,7 @@
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
@@ -41052,7 +41052,7 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -41083,7 +41083,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>2766-13-CM26</t>
+          <t>838108-27-CM26</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -41108,27 +41108,27 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K667" t="inlineStr"/>
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>3599.89</v>
+        <v>4157.6</v>
       </c>
     </row>
     <row r="668">
@@ -41510,7 +41510,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>3085-30-CM26</t>
+          <t>2766-13-CM26</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -41535,27 +41535,27 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>61.102.023-6</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OCTAVA LIMITADA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>76.046.716-2</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K674" t="inlineStr"/>
@@ -41565,7 +41565,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>1565.6</v>
+        <v>3599.89</v>
       </c>
     </row>
     <row r="675">
@@ -41906,7 +41906,7 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
@@ -41916,7 +41916,7 @@
       </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J680" t="inlineStr">
@@ -41937,7 +41937,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>838108-27-CM26</t>
+          <t>3085-30-CM26</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -41962,27 +41962,27 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.102.023-6</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>SOCIEDAD COMERCIAL OCTAVA LIMITADA</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.046.716-2</t>
         </is>
       </c>
       <c r="K681" t="inlineStr"/>
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>4157.6</v>
+        <v>1565.6</v>
       </c>
     </row>
     <row r="682">
@@ -42211,7 +42211,7 @@
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. Campo Militar "Antofagasta"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -42272,7 +42272,7 @@
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. Campo Militar "Antofagasta"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -42455,7 +42455,7 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>Superintendencia de Casinos de Juego</t>
+          <t>SUPERINTENDENCIA DE CASINOS DE JUEGO</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -42587,7 +42587,7 @@
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
@@ -42943,7 +42943,7 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -43248,7 +43248,7 @@
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -43370,7 +43370,7 @@
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="I706" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J706" t="inlineStr">
@@ -43563,7 +43563,7 @@
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
@@ -43736,7 +43736,7 @@
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Chiloé</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -43990,7 +43990,7 @@
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
@@ -44163,7 +44163,7 @@
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -44956,7 +44956,7 @@
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -45088,7 +45088,7 @@
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
@@ -45149,7 +45149,7 @@
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
@@ -45210,7 +45210,7 @@
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
@@ -45322,7 +45322,7 @@
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -45373,7 +45373,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
@@ -45505,7 +45505,7 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -45749,7 +45749,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -45810,7 +45810,7 @@
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
@@ -45932,7 +45932,7 @@
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -45993,7 +45993,7 @@
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -46054,7 +46054,7 @@
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -46552,7 +46552,7 @@
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
@@ -46796,7 +46796,7 @@
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
@@ -47101,7 +47101,7 @@
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
@@ -47518,7 +47518,7 @@
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LLANQUIHUE-DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
@@ -47579,7 +47579,7 @@
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FRE</t>
+          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FREI MONTALVA</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
@@ -47701,7 +47701,7 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
@@ -47823,7 +47823,7 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -47894,7 +47894,7 @@
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
@@ -48006,7 +48006,7 @@
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H780" t="inlineStr">
@@ -48128,7 +48128,7 @@
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
@@ -48433,7 +48433,7 @@
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
@@ -48464,7 +48464,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>4548-48-CM26</t>
+          <t>1208129-77-CM26</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -48484,32 +48484,32 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K788" t="inlineStr"/>
@@ -48519,13 +48519,13 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>1742.41</v>
+        <v>2659.08</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>2852-39-CM26</t>
+          <t>4548-48-CM26</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -48545,22 +48545,22 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -48580,7 +48580,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>2508.64</v>
+        <v>1742.41</v>
       </c>
     </row>
     <row r="790">
@@ -48616,7 +48616,7 @@
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H790" t="inlineStr">
@@ -48677,7 +48677,7 @@
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>CENTRAL ODONTOLOGICA IIA. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
@@ -48738,7 +48738,7 @@
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -48799,7 +48799,7 @@
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>JUZGADO DE GARANTIA DE COPIAPO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
@@ -48830,7 +48830,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>1208129-77-CM26</t>
+          <t>2852-39-CM26</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -48855,27 +48855,27 @@
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K794" t="inlineStr"/>
@@ -48885,7 +48885,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>2659.08</v>
+        <v>2508.64</v>
       </c>
     </row>
     <row r="795">
@@ -48952,7 +48952,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>1057513-38-CM26</t>
+          <t>1511-21-CM26</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -48977,27 +48977,27 @@
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>61.607.005-3</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J796" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K796" t="inlineStr"/>
@@ -49007,13 +49007,13 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>8044.93</v>
+        <v>6976.9</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>1511-21-CM26</t>
+          <t>5061-5-CM26</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -49033,32 +49033,32 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>comercial itahua.cl</t>
         </is>
       </c>
       <c r="J797" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>76.096.988-5</t>
         </is>
       </c>
       <c r="K797" t="inlineStr"/>
@@ -49068,13 +49068,13 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>6976.9</v>
+        <v>8068.82</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>5061-5-CM26</t>
+          <t>1057513-38-CM26</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -49094,32 +49094,32 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>61.607.005-3</t>
         </is>
       </c>
       <c r="G798" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>comercial itahua.cl</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>76.096.988-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K798" t="inlineStr"/>
@@ -49129,7 +49129,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>8068.82</v>
+        <v>8044.93</v>
       </c>
     </row>
     <row r="799">
@@ -49226,7 +49226,7 @@
       </c>
       <c r="G800" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H800" t="inlineStr">
@@ -49653,7 +49653,7 @@
       </c>
       <c r="G807" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H807" t="inlineStr">
@@ -49714,7 +49714,7 @@
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H808" t="inlineStr">
@@ -49806,7 +49806,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>2188-15-CM26</t>
+          <t>4777-52-CM26</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -49826,32 +49826,32 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>61.602.134-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J810" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K810" t="inlineStr"/>
@@ -49861,7 +49861,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>1903.23</v>
+        <v>5338.29</v>
       </c>
     </row>
     <row r="811">
@@ -49897,7 +49897,7 @@
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H811" t="inlineStr">
@@ -49928,7 +49928,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>4777-52-CM26</t>
+          <t>2188-15-CM26</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -49948,32 +49948,32 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.602.134-6</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K812" t="inlineStr"/>
@@ -49983,7 +49983,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>5338.29</v>
+        <v>1903.23</v>
       </c>
     </row>
     <row r="813">
@@ -50019,7 +50019,7 @@
       </c>
       <c r="G813" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H813" t="inlineStr">
@@ -50141,7 +50141,7 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H815" t="inlineStr">
@@ -50294,7 +50294,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>2555-4-CM26</t>
+          <t>1298355-56-CM26</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
@@ -50319,27 +50319,27 @@
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I818" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J818" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K818" t="inlineStr"/>
@@ -50349,13 +50349,13 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>2481.95</v>
+        <v>18182.96</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>1298355-56-CM26</t>
+          <t>2555-4-CM26</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -50380,27 +50380,27 @@
       </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G819" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K819" t="inlineStr"/>
@@ -50410,13 +50410,13 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>18182.96</v>
+        <v>2481.95</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>4477-7-CM26</t>
+          <t>1057374-61-CM26</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -50436,32 +50436,32 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>69.160.601-5</t>
+          <t>61.602.042-0</t>
         </is>
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA MANZANO S A</t>
         </is>
       </c>
       <c r="J820" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.908.760-k</t>
         </is>
       </c>
       <c r="K820" t="inlineStr"/>
@@ -50471,13 +50471,13 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>4152.47</v>
+        <v>26384.03</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>1691-182-CM26</t>
+          <t>4477-7-CM26</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -50497,32 +50497,32 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.160.601-5</t>
         </is>
       </c>
       <c r="G821" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J821" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K821" t="inlineStr"/>
@@ -50532,13 +50532,13 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>8021.7</v>
+        <v>4152.47</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>545598-31-CM26</t>
+          <t>1691-182-CM26</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -50563,27 +50563,27 @@
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>71.149.700-5</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I822" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K822" t="inlineStr"/>
@@ -50593,13 +50593,13 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>4227.96</v>
+        <v>8021.7</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>2912-48-CM26</t>
+          <t>545598-31-CM26</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -50619,17 +50619,17 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>69.220.702-5</t>
+          <t>71.149.700-5</t>
         </is>
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>CORP MUNICIPAL DE CASTRO PARA LA EDUCACION SALUD Y ATENCION AL MENOR</t>
         </is>
       </c>
       <c r="H823" t="inlineStr">
@@ -50654,13 +50654,13 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>27939.54</v>
+        <v>4227.96</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>5036-1-CM26</t>
+          <t>2912-48-CM26</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -50680,32 +50680,32 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>69.220.702-5</t>
         </is>
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I824" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K824" t="inlineStr"/>
@@ -50715,13 +50715,13 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>7722.66</v>
+        <v>27939.54</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>1260057-120-CM26</t>
+          <t>5036-1-CM26</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -50746,27 +50746,27 @@
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>61.602.121-4</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K825" t="inlineStr"/>
@@ -50776,13 +50776,13 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>8334.370000000001</v>
+        <v>7722.66</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>1357605-17-CM26</t>
+          <t>1260057-120-CM26</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
@@ -50802,32 +50802,32 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>71.186.200-5</t>
+          <t>61.602.121-4</t>
         </is>
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>Corporación Cultural de Antofagasta</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.592.530-4</t>
         </is>
       </c>
       <c r="K826" t="inlineStr"/>
@@ -50837,13 +50837,13 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>2867</v>
+        <v>8334.370000000001</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>881-6-CM26</t>
+          <t>1357605-17-CM26</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -50863,17 +50863,17 @@
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>71.186.200-5</t>
         </is>
       </c>
       <c r="G827" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>Corporación Cultural de Antofagasta</t>
         </is>
       </c>
       <c r="H827" t="inlineStr">
@@ -50883,12 +50883,12 @@
       </c>
       <c r="I827" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K827" t="inlineStr"/>
@@ -50898,13 +50898,13 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>842.62</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>881-2-CM26</t>
+          <t>881-6-CM26</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -50934,7 +50934,7 @@
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
@@ -50944,12 +50944,12 @@
       </c>
       <c r="I828" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J828" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K828" t="inlineStr"/>
@@ -50959,13 +50959,13 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>1204.97</v>
+        <v>842.62</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>2343-30-CM26</t>
+          <t>881-2-CM26</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -50990,27 +50990,27 @@
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I829" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K829" t="inlineStr"/>
@@ -51020,13 +51020,13 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>8118.88</v>
+        <v>1204.97</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>1078078-340-CM26</t>
+          <t>2343-30-CM26</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -51046,17 +51046,17 @@
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
@@ -51066,12 +51066,12 @@
       </c>
       <c r="I830" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K830" t="inlineStr"/>
@@ -51081,13 +51081,13 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>5459.34</v>
+        <v>8118.88</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>4433-4-CM26</t>
+          <t>1078078-340-CM26</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -51112,27 +51112,27 @@
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I831" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K831" t="inlineStr"/>
@@ -51142,7 +51142,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>7215.74</v>
+        <v>5459.34</v>
       </c>
     </row>
     <row r="832">
@@ -51544,7 +51544,7 @@
       </c>
       <c r="G838" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H838" t="inlineStr">
@@ -51615,7 +51615,7 @@
       </c>
       <c r="I839" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J839" t="inlineStr">
@@ -51666,7 +51666,7 @@
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H840" t="inlineStr">
@@ -51737,7 +51737,7 @@
       </c>
       <c r="I841" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J841" t="inlineStr">
@@ -52490,7 +52490,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>1057374-61-CM26</t>
+          <t>4433-4-CM26</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -52510,32 +52510,32 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>61.602.042-0</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA MANZANO S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>96.908.760-k</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K854" t="inlineStr"/>
@@ -52545,7 +52545,7 @@
         </is>
       </c>
       <c r="M854" s="2" t="n">
-        <v>26384.03</v>
+        <v>7215.74</v>
       </c>
     </row>
     <row r="855">
@@ -52703,7 +52703,7 @@
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>UNIDAD OPERATIVA DE CONTROL DE TRANSITO</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H857" t="inlineStr">
@@ -52886,7 +52886,7 @@
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H860" t="inlineStr">
@@ -53008,7 +53008,7 @@
       </c>
       <c r="G862" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H862" t="inlineStr">
@@ -53130,7 +53130,7 @@
       </c>
       <c r="G864" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H864" t="inlineStr">
@@ -53201,7 +53201,7 @@
       </c>
       <c r="I865" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J865" t="inlineStr">
@@ -53222,7 +53222,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>1422824-155-CM26</t>
+          <t>874750-22-CM26</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -53247,27 +53247,27 @@
       </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G866" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J866" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K866" t="inlineStr"/>
@@ -53277,7 +53277,7 @@
         </is>
       </c>
       <c r="M866" s="2" t="n">
-        <v>13494.39</v>
+        <v>9441.540000000001</v>
       </c>
     </row>
     <row r="867">
@@ -53618,7 +53618,7 @@
       </c>
       <c r="G872" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H872" t="inlineStr">
@@ -53649,7 +53649,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>874750-22-CM26</t>
+          <t>1422824-155-CM26</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -53674,27 +53674,27 @@
       </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G873" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J873" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>76.592.530-4</t>
         </is>
       </c>
       <c r="K873" t="inlineStr"/>
@@ -53704,7 +53704,7 @@
         </is>
       </c>
       <c r="M873" s="2" t="n">
-        <v>9441.540000000001</v>
+        <v>13494.39</v>
       </c>
     </row>
     <row r="874">
@@ -53750,7 +53750,7 @@
       </c>
       <c r="I874" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J874" t="inlineStr">
@@ -53801,7 +53801,7 @@
       </c>
       <c r="G875" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H875" t="inlineStr">
@@ -53954,7 +53954,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>1660-47-CM26</t>
+          <t>1660-46-CM26</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -53994,12 +53994,12 @@
       </c>
       <c r="I878" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J878" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K878" t="inlineStr"/>
@@ -54009,7 +54009,7 @@
         </is>
       </c>
       <c r="M878" s="2" t="n">
-        <v>2810.77</v>
+        <v>6434.86</v>
       </c>
     </row>
     <row r="879">
@@ -54106,7 +54106,7 @@
       </c>
       <c r="G880" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H880" t="inlineStr">
@@ -54167,7 +54167,7 @@
       </c>
       <c r="G881" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H881" t="inlineStr">
@@ -54259,7 +54259,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>1660-46-CM26</t>
+          <t>1660-47-CM26</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -54299,12 +54299,12 @@
       </c>
       <c r="I883" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J883" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K883" t="inlineStr"/>
@@ -54314,7 +54314,7 @@
         </is>
       </c>
       <c r="M883" s="2" t="n">
-        <v>6434.86</v>
+        <v>2810.77</v>
       </c>
     </row>
     <row r="884">
@@ -54472,7 +54472,7 @@
       </c>
       <c r="G886" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H886" t="inlineStr">
@@ -54533,7 +54533,7 @@
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H887" t="inlineStr">
@@ -54665,7 +54665,7 @@
       </c>
       <c r="I889" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J889" t="inlineStr">
@@ -54716,7 +54716,7 @@
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H890" t="inlineStr">
@@ -54808,7 +54808,7 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>4127-65-CM26</t>
+          <t>1079866-36-CM26</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
@@ -54833,12 +54833,12 @@
       </c>
       <c r="F892" t="inlineStr">
         <is>
-          <t>61.975.700-9</t>
+          <t>65.091.977-7</t>
         </is>
       </c>
       <c r="G892" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE REDES ASISTENCIALES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H892" t="inlineStr">
@@ -54848,12 +54848,12 @@
       </c>
       <c r="I892" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J892" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K892" t="inlineStr"/>
@@ -54863,13 +54863,13 @@
         </is>
       </c>
       <c r="M892" s="2" t="n">
-        <v>69822.14999999999</v>
+        <v>1747.19</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>1079866-36-CM26</t>
+          <t>1953-166-CM26</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
@@ -54894,27 +54894,27 @@
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t>65.091.977-7</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G893" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I893" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J893" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.202.065-3</t>
         </is>
       </c>
       <c r="K893" t="inlineStr"/>
@@ -54924,13 +54924,13 @@
         </is>
       </c>
       <c r="M893" s="2" t="n">
-        <v>1747.19</v>
+        <v>5873.29</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>1953-166-CM26</t>
+          <t>548864-10-CM26</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
@@ -54955,27 +54955,27 @@
       </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G894" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I894" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J894" t="inlineStr">
         <is>
-          <t>76.202.065-3</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K894" t="inlineStr"/>
@@ -54985,13 +54985,13 @@
         </is>
       </c>
       <c r="M894" s="2" t="n">
-        <v>5873.29</v>
+        <v>8605.440000000001</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>548864-10-CM26</t>
+          <t>3825-19-CM26</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -55016,27 +55016,27 @@
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G895" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J895" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K895" t="inlineStr"/>
@@ -55046,13 +55046,13 @@
         </is>
       </c>
       <c r="M895" s="2" t="n">
-        <v>8605.440000000001</v>
+        <v>17155.16</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>1067526-8-CM26</t>
+          <t>1346281-26-CM26</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
@@ -55077,27 +55077,27 @@
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G896" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J896" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K896" t="inlineStr"/>
@@ -55107,13 +55107,13 @@
         </is>
       </c>
       <c r="M896" s="2" t="n">
-        <v>10457.36</v>
+        <v>3920.72</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>1346281-26-CM26</t>
+          <t>1067526-8-CM26</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -55138,27 +55138,27 @@
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G897" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I897" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J897" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K897" t="inlineStr"/>
@@ -55168,7 +55168,7 @@
         </is>
       </c>
       <c r="M897" s="2" t="n">
-        <v>3920.72</v>
+        <v>10457.36</v>
       </c>
     </row>
     <row r="898">
@@ -55204,7 +55204,7 @@
       </c>
       <c r="G898" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H898" t="inlineStr">
@@ -55235,7 +55235,7 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>5110-5-CM26</t>
+          <t>2833-130-CM26</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
@@ -55260,27 +55260,27 @@
       </c>
       <c r="F899" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.930.600-7</t>
         </is>
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
         <is>
-          <t>JACKSON HOLE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J899" t="inlineStr">
         <is>
-          <t>78.057.703-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K899" t="inlineStr"/>
@@ -55290,13 +55290,13 @@
         </is>
       </c>
       <c r="M899" s="2" t="n">
-        <v>1368.26</v>
+        <v>3120.34</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>934-6-CM26</t>
+          <t>5110-5-CM26</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
@@ -55316,17 +55316,17 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G900" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H900" t="inlineStr">
@@ -55336,12 +55336,12 @@
       </c>
       <c r="I900" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JACKSON HOLE SPA</t>
         </is>
       </c>
       <c r="J900" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.057.703-7</t>
         </is>
       </c>
       <c r="K900" t="inlineStr"/>
@@ -55351,13 +55351,13 @@
         </is>
       </c>
       <c r="M900" s="2" t="n">
-        <v>2803.75</v>
+        <v>1368.26</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>3656-57-CM26</t>
+          <t>4127-65-CM26</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -55382,27 +55382,27 @@
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t>69.081.300-9</t>
+          <t>61.975.700-9</t>
         </is>
       </c>
       <c r="G901" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE REQUINOA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J901" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K901" t="inlineStr"/>
@@ -55412,13 +55412,13 @@
         </is>
       </c>
       <c r="M901" s="2" t="n">
-        <v>3022.97</v>
+        <v>69822.14999999999</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>3825-19-CM26</t>
+          <t>3656-57-CM26</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
@@ -55443,27 +55443,27 @@
       </c>
       <c r="F902" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>69.081.300-9</t>
         </is>
       </c>
       <c r="G902" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>I MUNICIPALIDAD DE REQUINOA</t>
         </is>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J902" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K902" t="inlineStr"/>
@@ -55473,13 +55473,13 @@
         </is>
       </c>
       <c r="M902" s="2" t="n">
-        <v>17155.16</v>
+        <v>3022.97</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>2341-46-CM26</t>
+          <t>2833-131-CM26</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -55504,27 +55504,27 @@
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>61.930.600-7</t>
         </is>
       </c>
       <c r="G903" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J903" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K903" t="inlineStr"/>
@@ -55534,13 +55534,13 @@
         </is>
       </c>
       <c r="M903" s="2" t="n">
-        <v>3577.11</v>
+        <v>2954.82</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>2215-67-CM26</t>
+          <t>934-6-CM26</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -55565,27 +55565,27 @@
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G904" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J904" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K904" t="inlineStr"/>
@@ -55595,13 +55595,13 @@
         </is>
       </c>
       <c r="M904" s="2" t="n">
-        <v>2620.92</v>
+        <v>2803.75</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>1611-13-CM26</t>
+          <t>1611-14-CM26</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -55631,7 +55631,7 @@
       </c>
       <c r="G905" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL CONSUMIDOR</t>
+          <t>Servicio Nacional del Consumidor - SERNAC</t>
         </is>
       </c>
       <c r="H905" t="inlineStr">
@@ -55641,12 +55641,12 @@
       </c>
       <c r="I905" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J905" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K905" t="inlineStr"/>
@@ -55656,13 +55656,13 @@
         </is>
       </c>
       <c r="M905" s="2" t="n">
-        <v>2563.81</v>
+        <v>1915.06</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>3512-74-CM26</t>
+          <t>2101-143-CM26</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
@@ -55682,32 +55682,32 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.602.213-k</t>
         </is>
       </c>
       <c r="G906" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>HOSPITAL INTERCULTURAL KALLVU LLANKA.-</t>
         </is>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I906" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J906" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K906" t="inlineStr"/>
@@ -55717,13 +55717,13 @@
         </is>
       </c>
       <c r="M906" s="2" t="n">
-        <v>20531.95</v>
+        <v>3727.27</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>1627-134-CM26</t>
+          <t>1611-13-CM26</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -55748,27 +55748,27 @@
       </c>
       <c r="F907" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>60.702.000-0</t>
         </is>
       </c>
       <c r="G907" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>Servicio Nacional del Consumidor - SERNAC</t>
         </is>
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J907" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K907" t="inlineStr"/>
@@ -55778,13 +55778,13 @@
         </is>
       </c>
       <c r="M907" s="2" t="n">
-        <v>26932.8</v>
+        <v>2563.81</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>1057532-148-CM26</t>
+          <t>3512-74-CM26</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
@@ -55804,32 +55804,32 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F908" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G908" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J908" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K908" t="inlineStr"/>
@@ -55839,13 +55839,13 @@
         </is>
       </c>
       <c r="M908" s="2" t="n">
-        <v>1108.98</v>
+        <v>20531.95</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>4177-11-CM26</t>
+          <t>1627-134-CM26</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
@@ -55870,27 +55870,27 @@
       </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J909" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K909" t="inlineStr"/>
@@ -55900,13 +55900,13 @@
         </is>
       </c>
       <c r="M909" s="2" t="n">
-        <v>9047.59</v>
+        <v>26932.8</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>1611-14-CM26</t>
+          <t>1057532-148-CM26</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
@@ -55931,27 +55931,27 @@
       </c>
       <c r="F910" t="inlineStr">
         <is>
-          <t>60.702.000-0</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G910" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL CONSUMIDOR</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I910" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J910" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K910" t="inlineStr"/>
@@ -55961,13 +55961,13 @@
         </is>
       </c>
       <c r="M910" s="2" t="n">
-        <v>1915.06</v>
+        <v>1108.98</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>3039-4-CM26</t>
+          <t>4177-11-CM26</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
@@ -55987,32 +55987,32 @@
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F911" t="inlineStr">
         <is>
-          <t>69.090.500-0</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G911" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOLOL</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H911" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I911" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J911" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K911" t="inlineStr"/>
@@ -56022,13 +56022,13 @@
         </is>
       </c>
       <c r="M911" s="2" t="n">
-        <v>3989.17</v>
+        <v>9047.59</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>2950-61-CM26</t>
+          <t>2215-67-CM26</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
@@ -56053,27 +56053,27 @@
       </c>
       <c r="F912" t="inlineStr">
         <is>
-          <t>61.102.010-4</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G912" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I912" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J912" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K912" t="inlineStr"/>
@@ -56083,13 +56083,13 @@
         </is>
       </c>
       <c r="M912" s="2" t="n">
-        <v>9922.82</v>
+        <v>2620.92</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>3882-27-CM26</t>
+          <t>3039-4-CM26</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -56109,32 +56109,32 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F913" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.090.500-0</t>
         </is>
       </c>
       <c r="G913" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE LOLOL</t>
         </is>
       </c>
       <c r="H913" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I913" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA INFINITO SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J913" t="inlineStr">
         <is>
-          <t>77.499.324-K</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K913" t="inlineStr"/>
@@ -56144,13 +56144,13 @@
         </is>
       </c>
       <c r="M913" s="2" t="n">
-        <v>8396.540000000001</v>
+        <v>3989.17</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>3378-1117-CM26</t>
+          <t>2950-61-CM26</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
@@ -56170,32 +56170,32 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F914" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.102.010-4</t>
         </is>
       </c>
       <c r="G914" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I914" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J914" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K914" t="inlineStr"/>
@@ -56205,13 +56205,13 @@
         </is>
       </c>
       <c r="M914" s="2" t="n">
-        <v>4031.13</v>
+        <v>9922.82</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>712830-7-CM26</t>
+          <t>3882-27-CM26</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -56231,32 +56231,32 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F915" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G915" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H915" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I915" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>COMERCIALIZADORA INFINITO SPA</t>
         </is>
       </c>
       <c r="J915" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>77.499.324-K</t>
         </is>
       </c>
       <c r="K915" t="inlineStr"/>
@@ -56266,13 +56266,13 @@
         </is>
       </c>
       <c r="M915" s="2" t="n">
-        <v>949.45</v>
+        <v>8396.540000000001</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>2101-143-CM26</t>
+          <t>3378-1117-CM26</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -56292,32 +56292,32 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F916" t="inlineStr">
         <is>
-          <t>61.602.213-k</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G916" t="inlineStr">
         <is>
-          <t>HOSPITAL INTERCULTURAL KALLVU LLANKA.-</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J916" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K916" t="inlineStr"/>
@@ -56327,13 +56327,13 @@
         </is>
       </c>
       <c r="M916" s="2" t="n">
-        <v>3727.27</v>
+        <v>4031.13</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>712830-6-CM26</t>
+          <t>712830-7-CM26</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -56373,12 +56373,12 @@
       </c>
       <c r="I917" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J917" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K917" t="inlineStr"/>
@@ -56388,13 +56388,13 @@
         </is>
       </c>
       <c r="M917" s="2" t="n">
-        <v>6497.49</v>
+        <v>949.45</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>1057389-454-CM26</t>
+          <t>2341-46-CM26</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -56414,32 +56414,32 @@
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G918" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J918" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K918" t="inlineStr"/>
@@ -56449,13 +56449,13 @@
         </is>
       </c>
       <c r="M918" s="2" t="n">
-        <v>2222.14</v>
+        <v>3577.11</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>1165648-18-CM26</t>
+          <t>712830-6-CM26</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -56480,27 +56480,27 @@
       </c>
       <c r="F919" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G919" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I919" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA MANZANO S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J919" t="inlineStr">
         <is>
-          <t>96.908.760-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K919" t="inlineStr"/>
@@ -56510,13 +56510,13 @@
         </is>
       </c>
       <c r="M919" s="2" t="n">
-        <v>2246.03</v>
+        <v>6497.49</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>3563-29-CM26</t>
+          <t>5153-193-CM26</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -56541,27 +56541,27 @@
       </c>
       <c r="F920" t="inlineStr">
         <is>
-          <t>69.252.100-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G920" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD TEODORO SCHMIDT</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H920" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I920" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J920" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K920" t="inlineStr"/>
@@ -56571,13 +56571,13 @@
         </is>
       </c>
       <c r="M920" s="2" t="n">
-        <v>3364.94</v>
+        <v>3308.35</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>3559-16-CM26</t>
+          <t>3385-14-CM26</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
@@ -56597,17 +56597,17 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F921" t="inlineStr">
         <is>
-          <t>69.110.800-7</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G921" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCAHUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H921" t="inlineStr">
@@ -56617,12 +56617,12 @@
       </c>
       <c r="I921" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J921" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K921" t="inlineStr"/>
@@ -56632,13 +56632,13 @@
         </is>
       </c>
       <c r="M921" s="2" t="n">
-        <v>6865.25</v>
+        <v>2975.41</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>4375-104-CM26</t>
+          <t>3563-29-CM26</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
@@ -56658,32 +56658,32 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F922" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>69.252.100-5</t>
         </is>
       </c>
       <c r="G922" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>ILUSTRE MUNICIPALIDAD TEODORO SCHMIDT</t>
         </is>
       </c>
       <c r="H922" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J922" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K922" t="inlineStr"/>
@@ -56693,13 +56693,13 @@
         </is>
       </c>
       <c r="M922" s="2" t="n">
-        <v>50798.01</v>
+        <v>3364.94</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>4375-130-CM26</t>
+          <t>3559-16-CM26</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -56719,32 +56719,32 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F923" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>69.110.800-7</t>
         </is>
       </c>
       <c r="G923" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>I MUNICIPALIDAD DE PENCAHUE</t>
         </is>
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J923" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>76.097.502-8</t>
         </is>
       </c>
       <c r="K923" t="inlineStr"/>
@@ -56754,13 +56754,13 @@
         </is>
       </c>
       <c r="M923" s="2" t="n">
-        <v>5037.52</v>
+        <v>6865.25</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>4375-132-CM26</t>
+          <t>4375-104-CM26</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -56815,13 +56815,13 @@
         </is>
       </c>
       <c r="M924" s="2" t="n">
-        <v>10386.97</v>
+        <v>50798.01</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>4375-152-CM26</t>
+          <t>4375-130-CM26</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -56876,13 +56876,13 @@
         </is>
       </c>
       <c r="M925" s="2" t="n">
-        <v>8851.5</v>
+        <v>5037.52</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>1709-15-CM26</t>
+          <t>4375-132-CM26</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -56907,27 +56907,27 @@
       </c>
       <c r="F926" t="inlineStr">
         <is>
-          <t>69.120.400-6</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CAUQUENES</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J926" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K926" t="inlineStr"/>
@@ -56937,13 +56937,13 @@
         </is>
       </c>
       <c r="M926" s="2" t="n">
-        <v>39286.01</v>
+        <v>10386.97</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>623-36-CM26</t>
+          <t>4375-152-CM26</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -56968,27 +56968,27 @@
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I927" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J927" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K927" t="inlineStr"/>
@@ -56998,13 +56998,13 @@
         </is>
       </c>
       <c r="M927" s="2" t="n">
-        <v>11427.4</v>
+        <v>8851.5</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>1430710-63-CM26</t>
+          <t>1709-15-CM26</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
@@ -57024,32 +57024,32 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F928" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.120.400-6</t>
         </is>
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE CAUQUENES</t>
         </is>
       </c>
       <c r="H928" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I928" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J928" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K928" t="inlineStr"/>
@@ -57059,13 +57059,13 @@
         </is>
       </c>
       <c r="M928" s="2" t="n">
-        <v>3688.45</v>
+        <v>39286.01</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>5153-192-CM26</t>
+          <t>623-36-CM26</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -57085,17 +57085,17 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F929" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G929" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H929" t="inlineStr">
@@ -57105,12 +57105,12 @@
       </c>
       <c r="I929" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J929" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K929" t="inlineStr"/>
@@ -57120,13 +57120,13 @@
         </is>
       </c>
       <c r="M929" s="2" t="n">
-        <v>3462.36</v>
+        <v>11427.4</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>5153-193-CM26</t>
+          <t>1430710-63-CM26</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
@@ -57151,27 +57151,27 @@
       </c>
       <c r="F930" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H930" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I930" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J930" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K930" t="inlineStr"/>
@@ -57181,13 +57181,13 @@
         </is>
       </c>
       <c r="M930" s="2" t="n">
-        <v>3308.35</v>
+        <v>3688.45</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>5153-194-CM26</t>
+          <t>1057389-454-CM26</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -57207,32 +57207,32 @@
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F931" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G931" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H931" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I931" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J931" t="inlineStr">
         <is>
-          <t>76.202.065-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K931" t="inlineStr"/>
@@ -57242,13 +57242,13 @@
         </is>
       </c>
       <c r="M931" s="2" t="n">
-        <v>9877.639999999999</v>
+        <v>2222.14</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>3311-4-CM26</t>
+          <t>5153-192-CM26</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
@@ -57268,32 +57268,32 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F932" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H932" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I932" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J932" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K932" t="inlineStr"/>
@@ -57303,13 +57303,13 @@
         </is>
       </c>
       <c r="M932" s="2" t="n">
-        <v>3145.1</v>
+        <v>3462.36</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>1057496-203-CM26</t>
+          <t>5153-194-CM26</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -57329,17 +57329,17 @@
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F933" t="inlineStr">
         <is>
-          <t>61.608.105-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR HOSPITAL SAN LUIS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
@@ -57349,12 +57349,12 @@
       </c>
       <c r="I933" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J933" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.202.065-3</t>
         </is>
       </c>
       <c r="K933" t="inlineStr"/>
@@ -57364,13 +57364,13 @@
         </is>
       </c>
       <c r="M933" s="2" t="n">
-        <v>1397.62</v>
+        <v>9877.639999999999</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>1208129-73-CM26</t>
+          <t>2833-129-CM26</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
@@ -57390,32 +57390,32 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F934" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.930.600-7</t>
         </is>
       </c>
       <c r="G934" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H934" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I934" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J934" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K934" t="inlineStr"/>
@@ -57425,13 +57425,13 @@
         </is>
       </c>
       <c r="M934" s="2" t="n">
-        <v>2691.85</v>
+        <v>5984.64</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>2018-20-CM26</t>
+          <t>3311-4-CM26</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -57456,27 +57456,27 @@
       </c>
       <c r="F935" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H935" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I935" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="J935" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="K935" t="inlineStr"/>
@@ -57486,13 +57486,13 @@
         </is>
       </c>
       <c r="M935" s="2" t="n">
-        <v>5809.5</v>
+        <v>3145.1</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>4856-13-CM26</t>
+          <t>1208129-73-CM26</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
@@ -57517,12 +57517,12 @@
       </c>
       <c r="F936" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G936" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H936" t="inlineStr">
@@ -57532,12 +57532,12 @@
       </c>
       <c r="I936" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OCTAVA LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J936" t="inlineStr">
         <is>
-          <t>76.046.716-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K936" t="inlineStr"/>
@@ -57547,13 +57547,13 @@
         </is>
       </c>
       <c r="M936" s="2" t="n">
-        <v>4028.95</v>
+        <v>2691.85</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>3209-12-CM26</t>
+          <t>2018-20-CM26</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -57573,32 +57573,32 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F937" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G937" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H937" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I937" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J937" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K937" t="inlineStr"/>
@@ -57608,13 +57608,13 @@
         </is>
       </c>
       <c r="M937" s="2" t="n">
-        <v>8748.799999999999</v>
+        <v>5809.5</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>2082-2-CM26</t>
+          <t>4856-13-CM26</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
@@ -57639,27 +57639,27 @@
       </c>
       <c r="F938" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G938" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H938" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I938" t="inlineStr">
         <is>
-          <t>GRUPO DK SERVICIOS LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL OCTAVA LIMITADA</t>
         </is>
       </c>
       <c r="J938" t="inlineStr">
         <is>
-          <t>76.556.184-1</t>
+          <t>76.046.716-2</t>
         </is>
       </c>
       <c r="K938" t="inlineStr"/>
@@ -57669,13 +57669,13 @@
         </is>
       </c>
       <c r="M938" s="2" t="n">
-        <v>9306.08</v>
+        <v>4028.95</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>881-4-CM26</t>
+          <t>3209-12-CM26</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
@@ -57695,32 +57695,32 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F939" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G939" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H939" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I939" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J939" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K939" t="inlineStr"/>
@@ -57730,13 +57730,13 @@
         </is>
       </c>
       <c r="M939" s="2" t="n">
-        <v>826.12</v>
+        <v>8748.799999999999</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>4473-22-CM26</t>
+          <t>2082-2-CM26</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
@@ -57761,27 +57761,27 @@
       </c>
       <c r="F940" t="inlineStr">
         <is>
-          <t>69.100.200-4</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G940" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H940" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I940" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>GRUPO DK SERVICIOS LIMITADA</t>
         </is>
       </c>
       <c r="J940" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>76.556.184-1</t>
         </is>
       </c>
       <c r="K940" t="inlineStr"/>
@@ -57791,13 +57791,13 @@
         </is>
       </c>
       <c r="M940" s="2" t="n">
-        <v>14825.48</v>
+        <v>9306.08</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>1057414-78-CM26</t>
+          <t>881-4-CM26</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
@@ -57822,27 +57822,27 @@
       </c>
       <c r="F941" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G941" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H941" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I941" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J941" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K941" t="inlineStr"/>
@@ -57852,13 +57852,13 @@
         </is>
       </c>
       <c r="M941" s="2" t="n">
-        <v>20325.75</v>
+        <v>826.12</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>938614-7378-CM26</t>
+          <t>4473-22-CM26</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
@@ -57883,27 +57883,27 @@
       </c>
       <c r="F942" t="inlineStr">
         <is>
-          <t>65.124.882-5</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G942" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H942" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I942" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J942" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K942" t="inlineStr"/>
@@ -57913,13 +57913,13 @@
         </is>
       </c>
       <c r="M942" s="2" t="n">
-        <v>2436.79</v>
+        <v>14825.48</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>1057531-44-CM26</t>
+          <t>1057414-78-CM26</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
@@ -57944,17 +57944,17 @@
       </c>
       <c r="F943" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H943" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I943" t="inlineStr">
@@ -57974,13 +57974,13 @@
         </is>
       </c>
       <c r="M943" s="2" t="n">
-        <v>2969.78</v>
+        <v>20325.75</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>1057531-45-CM26</t>
+          <t>938614-7378-CM26</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
@@ -58005,27 +58005,27 @@
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>65.124.882-5</t>
         </is>
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H944" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I944" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J944" t="inlineStr">
         <is>
-          <t>78.307.160-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K944" t="inlineStr"/>
@@ -58035,13 +58035,13 @@
         </is>
       </c>
       <c r="M944" s="2" t="n">
-        <v>4022.79</v>
+        <v>2436.79</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>3385-14-CM26</t>
+          <t>1057531-44-CM26</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
@@ -58066,27 +58066,27 @@
       </c>
       <c r="F945" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I945" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J945" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K945" t="inlineStr"/>
@@ -58096,13 +58096,13 @@
         </is>
       </c>
       <c r="M945" s="2" t="n">
-        <v>2975.41</v>
+        <v>2969.78</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>3512-92-CM26</t>
+          <t>1057531-45-CM26</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
@@ -58122,32 +58122,32 @@
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F946" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H946" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I946" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD COMERCIAL OFIMASTER  SPA</t>
         </is>
       </c>
       <c r="J946" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>78.307.160-6</t>
         </is>
       </c>
       <c r="K946" t="inlineStr"/>
@@ -58157,6 +58157,189 @@
         </is>
       </c>
       <c r="M946" s="2" t="n">
+        <v>4022.79</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>1165648-18-CM26</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>69.061.100-7</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA MANZANO S A</t>
+        </is>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>96.908.760-k</t>
+        </is>
+      </c>
+      <c r="K947" t="inlineStr"/>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M947" s="2" t="n">
+        <v>2246.03</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>1057496-203-CM26</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>61.608.105-5</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR HOSPITAL SAN LUIS</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K948" t="inlineStr"/>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M948" s="2" t="n">
+        <v>1397.62</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>3512-92-CM26</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K949" t="inlineStr"/>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M949" s="2" t="n">
         <v>904.37</v>
       </c>
     </row>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>77.934.122-4</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1387,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1513,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1639,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1765,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2074,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2383,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2509,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2635,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2700,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2765,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2891,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2956,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3021,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3086,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3151,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3277,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3403,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3468,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3533,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3598,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3663,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3789,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4098,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4163,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4228,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4293,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4480,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4606,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4732,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4797,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4923,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4988,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5053,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5118,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5183,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5309,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5374,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5439,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5504,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5569,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5634,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5699,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5764,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5890,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5955,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6264,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6329,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6394,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6459,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6524,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6650,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6715,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6780,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6845,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6971,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7036,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7101,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7166,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7231,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7357,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7483,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7548,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7613,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7678,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7743,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7869,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7934,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7999,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8064,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8129,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8316,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8381,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8507,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8572,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8698,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8763,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8828,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8954,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9019,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9084,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9149,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9214,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9401,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9466,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9531,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9596,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9661,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9726,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9791,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9856,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9982,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10047,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10112,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10177,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10242,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10307,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10372,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10437,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10502,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10628,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10754,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10819,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +10949,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11014,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +11140,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11205,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11270,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11335,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11400,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11465,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11530,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11595,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11721,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11847,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +11912,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +11977,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12042,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12168,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12233,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12359,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12424,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12550,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12615,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12741,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +12806,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +12871,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +12936,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +13001,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +13066,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13131,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13196,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13261,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13326,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13391,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13517,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13582,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +13891,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +14017,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13498,7 +14082,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +14147,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14212,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14277,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13864,7 +14464,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14529,11 @@
           <t>78.106.527-7</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14108,7 +14716,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +14781,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14230,7 +14846,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +14911,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +14976,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +15041,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +15167,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15354,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14779,7 +15419,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15484,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15549,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15614,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15679,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +15744,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +15809,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15206,7 +15874,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +16061,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15450,7 +16126,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15511,7 +16191,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15694,7 +16378,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16626,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +16691,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +16817,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16243,7 +16943,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +17008,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +17073,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16426,7 +17138,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16487,7 +17203,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16548,7 +17268,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16731,7 +17455,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16792,7 +17520,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16853,7 +17585,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16914,7 +17650,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16975,7 +17715,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17036,7 +17780,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17219,7 +17967,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17341,7 +18093,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17402,7 +18158,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17463,7 +18223,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17524,7 +18288,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +18353,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17646,7 +18418,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17829,7 +18605,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17951,7 +18731,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18012,7 +18796,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18073,7 +18861,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18134,7 +18926,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18195,7 +18991,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18256,7 +19056,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18317,7 +19121,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18439,7 +19247,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +19434,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18683,7 +19499,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18805,7 +19625,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +19690,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18927,7 +19755,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18988,7 +19820,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19049,7 +19885,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19110,7 +19950,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +20015,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +20080,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19354,7 +20206,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +20271,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +20336,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +20401,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19659,7 +20527,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19720,7 +20592,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +20657,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19842,7 +20722,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +20787,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +20852,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20086,7 +20978,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20147,7 +21043,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20208,7 +21108,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20391,7 +21295,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21421,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20574,7 +21486,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21551,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21616,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20757,7 +21681,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +21746,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20879,7 +21811,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +21876,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21001,7 +21941,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21062,7 +22006,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +22071,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21184,7 +22136,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +22262,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +22327,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21428,7 +22392,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21611,7 +22579,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21672,7 +22644,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21733,7 +22709,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21855,7 +22835,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21916,7 +22900,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21977,7 +22965,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22038,7 +23030,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22099,7 +23095,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22160,7 +23160,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22221,7 +23225,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22282,7 +23290,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22343,7 +23355,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22404,7 +23420,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22465,7 +23485,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22587,7 +23611,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +23737,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22770,7 +23802,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22831,7 +23867,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23014,7 +24054,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23075,7 +24119,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23136,7 +24184,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23258,7 +24310,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23319,7 +24375,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23380,7 +24440,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23563,7 +24627,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23868,7 +24936,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23929,7 +25001,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23990,7 +25066,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24051,7 +25131,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24112,7 +25196,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24173,7 +25261,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24295,7 +25387,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24417,7 +25513,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24478,7 +25578,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24600,7 +25704,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24661,7 +25769,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24722,7 +25834,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24905,7 +26021,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25088,7 +26208,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25149,7 +26273,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25210,7 +26338,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25332,7 +26464,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25393,7 +26529,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25454,7 +26594,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25515,7 +26659,11 @@
           <t>77.577.274-3</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25576,7 +26724,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25637,7 +26789,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25698,7 +26854,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25759,7 +26919,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25820,7 +26984,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25942,7 +27110,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26003,7 +27175,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26064,7 +27240,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26125,7 +27305,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26186,7 +27370,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26247,7 +27435,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26308,7 +27500,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26369,7 +27565,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26491,7 +27691,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26552,7 +27756,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26613,7 +27821,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26735,7 +27947,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26796,7 +28012,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26857,7 +28077,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26918,7 +28142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26979,7 +28207,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27040,7 +28272,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27101,7 +28337,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27162,7 +28402,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27223,7 +28467,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27345,7 +28593,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27406,7 +28658,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27467,7 +28723,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27528,7 +28788,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27589,7 +28853,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27711,7 +28979,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27833,7 +29105,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27894,7 +29170,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +29235,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28016,7 +29300,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28077,7 +29365,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28138,7 +29430,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28260,7 +29556,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28321,7 +29621,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28382,7 +29686,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28443,7 +29751,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28504,7 +29816,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28565,7 +29881,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28626,7 +29946,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28687,7 +30011,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28809,7 +30137,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28870,7 +30202,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28931,7 +30267,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28992,7 +30332,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29053,7 +30397,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29114,7 +30462,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29175,7 +30527,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29236,7 +30592,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29297,7 +30657,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29358,7 +30722,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29419,7 +30787,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29480,7 +30852,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +30917,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +30982,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29663,7 +31047,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29846,7 +31234,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29968,7 +31360,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +31425,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +31551,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +31616,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30273,7 +31681,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30334,7 +31746,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +31872,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +31998,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +32063,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +32128,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +32254,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +32807,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31432,7 +32872,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +32998,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33185,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31859,7 +33311,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31920,7 +33376,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +33441,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32042,7 +33506,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +33571,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32347,7 +33819,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32469,7 +33945,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32530,7 +34010,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32591,7 +34075,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32652,7 +34140,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32713,7 +34205,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32774,7 +34270,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32896,7 +34396,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32957,7 +34461,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33140,7 +34648,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33201,7 +34713,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33262,7 +34778,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33323,7 +34843,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33384,7 +34908,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33445,7 +34973,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33567,7 +35099,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33628,7 +35164,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33750,7 +35290,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33933,7 +35477,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33994,7 +35542,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34055,7 +35607,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34116,7 +35672,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34177,7 +35737,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34238,7 +35802,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34360,7 +35928,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34421,7 +35993,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34543,7 +36119,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36184,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34665,7 +36249,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34726,7 +36314,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +36379,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34848,7 +36444,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34909,7 +36509,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35092,7 +36696,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35153,7 +36761,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35275,7 +36887,11 @@
           <t>76.539.061-3</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35336,7 +36952,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35397,7 +37017,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35458,7 +37082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35519,7 +37147,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35580,7 +37212,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35641,7 +37277,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35702,7 +37342,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35824,7 +37468,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35946,7 +37594,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36007,7 +37659,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36068,7 +37724,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +37789,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36190,7 +37854,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36251,7 +37919,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +37984,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36434,7 +38110,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36495,7 +38175,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36556,7 +38240,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36617,7 +38305,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36739,7 +38431,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36800,7 +38496,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36861,7 +38561,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36983,7 +38687,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37044,7 +38752,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37166,7 +38878,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37227,7 +38943,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37288,7 +39008,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37349,7 +39073,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37532,7 +39260,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37593,7 +39325,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +39390,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37715,7 +39455,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37776,7 +39520,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37837,7 +39585,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37959,7 +39711,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38020,7 +39776,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38142,7 +39902,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38203,7 +39967,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38264,7 +40032,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38325,7 +40097,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +40162,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40288,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38569,7 +40353,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38630,7 +40418,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +40483,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +40548,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38874,7 +40674,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +40739,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39057,7 +40865,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39118,7 +40930,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39240,7 +41056,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39301,7 +41121,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39362,7 +41186,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39484,7 +41312,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39545,7 +41377,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39667,7 +41503,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39728,7 +41568,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39789,7 +41633,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39850,7 +41698,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39911,7 +41763,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39972,7 +41828,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40033,7 +41893,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40094,7 +41958,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40155,7 +42023,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40216,7 +42088,11 @@
           <t>77.045.877-3</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40277,7 +42153,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40399,7 +42279,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40460,7 +42344,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40582,7 +42470,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40643,7 +42535,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40765,7 +42661,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40826,7 +42726,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40887,7 +42791,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40948,7 +42856,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41009,7 +42921,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41253,7 +43169,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41314,7 +43234,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41375,7 +43299,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41436,7 +43364,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41497,7 +43429,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41619,7 +43555,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41680,7 +43620,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41741,7 +43685,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41863,7 +43811,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41924,7 +43876,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42168,7 +44124,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42229,7 +44189,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42290,7 +44254,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42351,7 +44319,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42473,7 +44445,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42534,7 +44510,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42595,7 +44575,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42656,7 +44640,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42778,7 +44766,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42839,7 +44831,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42961,7 +44957,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43022,7 +45022,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43144,7 +45148,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43205,7 +45213,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43266,7 +45278,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43327,7 +45343,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43449,7 +45469,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43510,7 +45534,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43571,7 +45599,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43693,7 +45725,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43754,7 +45790,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43815,7 +45855,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43876,7 +45920,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43937,7 +45985,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43998,7 +46050,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44059,7 +46115,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44120,7 +46180,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44181,7 +46245,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44303,7 +46371,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44425,7 +46497,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44486,7 +46562,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44608,7 +46688,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44669,7 +46753,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44730,7 +46818,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44791,7 +46883,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44852,7 +46948,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44913,7 +47013,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44974,7 +47078,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45035,7 +47143,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45157,7 +47269,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45340,7 +47456,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45401,7 +47521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45462,7 +47586,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45523,7 +47651,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45584,7 +47716,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45645,7 +47781,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45767,7 +47907,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45828,7 +47972,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45889,7 +48037,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46072,7 +48224,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46133,7 +48289,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46194,7 +48354,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46255,7 +48419,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46316,7 +48484,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46377,7 +48549,11 @@
           <t>77.045.877-3</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46438,7 +48614,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46499,7 +48679,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46621,7 +48805,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46682,7 +48870,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46743,7 +48935,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46865,7 +49061,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47048,7 +49248,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47231,7 +49435,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47292,7 +49500,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47353,7 +49565,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47414,7 +49630,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L770" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47475,7 +49695,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47597,7 +49821,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47658,7 +49886,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K774" t="inlineStr"/>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L774" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47719,7 +49951,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L775" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47780,7 +50016,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L776" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47902,7 +50142,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K778" t="inlineStr"/>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L778" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47963,7 +50207,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48085,7 +50333,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K781" t="inlineStr"/>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L781" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48146,7 +50398,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L782" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48268,7 +50524,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K784" t="inlineStr"/>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L784" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48329,7 +50589,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48390,7 +50654,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K786" t="inlineStr"/>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L786" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48451,7 +50719,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K787" t="inlineStr"/>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L787" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48512,7 +50784,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K788" t="inlineStr"/>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L788" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48573,7 +50849,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K789" t="inlineStr"/>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L789" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48634,7 +50914,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48695,7 +50979,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48817,7 +51105,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L793" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48878,7 +51170,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48939,7 +51235,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L795" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49000,7 +51300,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L796" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49183,7 +51487,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K799" t="inlineStr"/>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L799" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49305,7 +51613,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49366,7 +51678,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L802" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49427,7 +51743,11 @@
           <t>77.020.146-2</t>
         </is>
       </c>
-      <c r="K803" t="inlineStr"/>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L803" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49488,7 +51808,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L804" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49549,7 +51873,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L805" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49610,7 +51938,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49732,7 +52064,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K808" t="inlineStr"/>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L808" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49854,7 +52190,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K810" t="inlineStr"/>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L810" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49976,7 +52316,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K812" t="inlineStr"/>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L812" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50037,7 +52381,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K813" t="inlineStr"/>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L813" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50098,7 +52446,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50159,7 +52511,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K815" t="inlineStr"/>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L815" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50220,7 +52576,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K816" t="inlineStr"/>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L816" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50281,7 +52641,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K817" t="inlineStr"/>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L817" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50342,7 +52706,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K818" t="inlineStr"/>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L818" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50525,7 +52893,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K821" t="inlineStr"/>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L821" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50647,7 +53019,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K823" t="inlineStr"/>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L823" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50708,7 +53084,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K824" t="inlineStr"/>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L824" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50891,7 +53271,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K827" t="inlineStr"/>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L827" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50952,7 +53336,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K828" t="inlineStr"/>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L828" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51013,7 +53401,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K829" t="inlineStr"/>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L829" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51074,7 +53466,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K830" t="inlineStr"/>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L830" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51318,7 +53714,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K834" t="inlineStr"/>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L834" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51379,7 +53779,11 @@
           <t>77.478.598-1</t>
         </is>
       </c>
-      <c r="K835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L835" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51501,7 +53905,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K837" t="inlineStr"/>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L837" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51562,7 +53970,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L838" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51684,7 +54096,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K840" t="inlineStr"/>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L840" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51928,7 +54344,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K844" t="inlineStr"/>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L844" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51989,7 +54409,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K845" t="inlineStr"/>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L845" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52050,7 +54474,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K846" t="inlineStr"/>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L846" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52111,7 +54539,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K847" t="inlineStr"/>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L847" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52172,7 +54604,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K848" t="inlineStr"/>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L848" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52233,7 +54669,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K849" t="inlineStr"/>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L849" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52355,7 +54795,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K851" t="inlineStr"/>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L851" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52416,7 +54860,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K852" t="inlineStr"/>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L852" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52477,7 +54925,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K853" t="inlineStr"/>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L853" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52538,7 +54990,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K854" t="inlineStr"/>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L854" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52599,7 +55055,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K855" t="inlineStr"/>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L855" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52660,7 +55120,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K856" t="inlineStr"/>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L856" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52721,7 +55185,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K857" t="inlineStr"/>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L857" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52782,7 +55250,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K858" t="inlineStr"/>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L858" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52843,7 +55315,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K859" t="inlineStr"/>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L859" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52965,7 +55441,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K861" t="inlineStr"/>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L861" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53087,7 +55567,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K863" t="inlineStr"/>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L863" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53148,7 +55632,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K864" t="inlineStr"/>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L864" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53270,7 +55758,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K866" t="inlineStr"/>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L866" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53331,7 +55823,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K867" t="inlineStr"/>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L867" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53392,7 +55888,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K868" t="inlineStr"/>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L868" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53453,7 +55953,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K869" t="inlineStr"/>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L869" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53636,7 +56140,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K872" t="inlineStr"/>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L872" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53819,7 +56327,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K875" t="inlineStr"/>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L875" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53880,7 +56392,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K876" t="inlineStr"/>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L876" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53941,7 +56457,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K877" t="inlineStr"/>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L877" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54002,7 +56522,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K878" t="inlineStr"/>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L878" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54124,7 +56648,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K880" t="inlineStr"/>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L880" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54185,7 +56713,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K881" t="inlineStr"/>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L881" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54246,7 +56778,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K882" t="inlineStr"/>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L882" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54307,7 +56843,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L883" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54368,7 +56908,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K884" t="inlineStr"/>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L884" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54429,7 +56973,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K885" t="inlineStr"/>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L885" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54490,7 +57038,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K886" t="inlineStr"/>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L886" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54551,7 +57103,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K887" t="inlineStr"/>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L887" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54612,7 +57168,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K888" t="inlineStr"/>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L888" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54795,7 +57355,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K891" t="inlineStr"/>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L891" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54856,7 +57420,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K892" t="inlineStr"/>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L892" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54917,7 +57485,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K893" t="inlineStr"/>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L893" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54978,7 +57550,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K894" t="inlineStr"/>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L894" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55039,7 +57615,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K895" t="inlineStr"/>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L895" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55100,7 +57680,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K896" t="inlineStr"/>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L896" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55161,7 +57745,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K897" t="inlineStr"/>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L897" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55222,7 +57810,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K898" t="inlineStr"/>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L898" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55283,7 +57875,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K899" t="inlineStr"/>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L899" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55344,7 +57940,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K900" t="inlineStr"/>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L900" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55405,7 +58005,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L901" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55466,7 +58070,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L902" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55527,7 +58135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K903" t="inlineStr"/>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L903" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55588,7 +58200,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K904" t="inlineStr"/>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L904" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55649,7 +58265,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K905" t="inlineStr"/>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L905" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55710,7 +58330,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K906" t="inlineStr"/>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L906" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55771,7 +58395,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L907" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55832,7 +58460,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K908" t="inlineStr"/>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L908" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55893,7 +58525,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K909" t="inlineStr"/>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L909" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55954,7 +58590,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L910" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56076,7 +58716,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K912" t="inlineStr"/>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L912" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56259,7 +58903,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K915" t="inlineStr"/>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L915" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56320,7 +58968,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K916" t="inlineStr"/>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L916" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56381,7 +59033,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K917" t="inlineStr"/>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L917" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56442,7 +59098,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K918" t="inlineStr"/>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L918" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56503,7 +59163,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K919" t="inlineStr"/>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L919" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56564,7 +59228,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K920" t="inlineStr"/>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L920" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56625,7 +59293,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K921" t="inlineStr"/>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L921" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56686,7 +59358,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L922" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56808,7 +59484,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K924" t="inlineStr"/>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L924" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56869,7 +59549,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr"/>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L925" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56930,7 +59614,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K926" t="inlineStr"/>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L926" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56991,7 +59679,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K927" t="inlineStr"/>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L927" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57052,7 +59744,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr"/>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L928" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57113,7 +59809,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K929" t="inlineStr"/>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L929" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57235,7 +59935,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K931" t="inlineStr"/>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L931" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57357,7 +60061,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K933" t="inlineStr"/>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L933" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57418,7 +60126,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K934" t="inlineStr"/>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L934" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57540,7 +60252,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K936" t="inlineStr"/>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L936" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57601,7 +60317,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K937" t="inlineStr"/>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L937" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57723,7 +60443,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr"/>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L939" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57784,7 +60508,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K940" t="inlineStr"/>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L940" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57845,7 +60573,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K941" t="inlineStr"/>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L941" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57906,7 +60638,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K942" t="inlineStr"/>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L942" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57967,7 +60703,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L943" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58028,7 +60768,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K944" t="inlineStr"/>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L944" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58089,7 +60833,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K945" t="inlineStr"/>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L945" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58333,7 +61081,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K949" t="inlineStr"/>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L949" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2026.xlsx
@@ -879,7 +879,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2830,7 +2834,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3216,7 +3224,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3915,7 +3927,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4358,7 +4374,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4862,7 +4882,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12298,7 +12322,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14655,7 +14683,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15939,7 +15971,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16504,7 +16540,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17394,7 +17434,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17906,7 +17950,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18032,7 +18080,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19373,7 +19425,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21360,7 +21416,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22774,7 +22834,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24875,7 +24939,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25899,7 +25967,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26086,7 +26158,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27886,7 +27962,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28532,7 +28612,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29495,7 +29579,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32502,7 +32590,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32624,7 +32716,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34587,7 +34683,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36058,7 +36158,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36574,7 +36678,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37407,7 +37515,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42600,7 +42712,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43047,7 +43163,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47208,7 +47328,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48744,7 +48868,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49000,7 +49128,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49313,7 +49445,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51426,7 +51562,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L798" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52771,7 +52911,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K819" t="inlineStr"/>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L819" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54035,7 +54179,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K839" t="inlineStr"/>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L839" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54161,7 +54309,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K841" t="inlineStr"/>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L841" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57233,7 +57385,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K889" t="inlineStr"/>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L889" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58842,7 +58998,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L914" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61020,7 +61180,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K948" t="inlineStr"/>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L948" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2026.xlsx
@@ -15553,7 +15553,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -34273,7 +34273,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
@@ -41140,7 +41140,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
@@ -46910,7 +46910,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
